--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-97.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -515,18 +515,18 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>398</v>
       </c>
       <c r="K2" t="n">
-        <v>398</v>
+        <v>-75252</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-100.5%</t>
         </is>
       </c>
     </row>
@@ -597,16 +597,16 @@
         <v>280000</v>
       </c>
       <c r="D4" t="n">
-        <v>46390</v>
+        <v>52990</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+4.5%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>42390</v>
+        <v>48990</v>
       </c>
       <c r="K4" t="n">
-        <v>40996</v>
+        <v>60996</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>-19.7%</t>
         </is>
       </c>
     </row>
@@ -649,16 +649,16 @@
         <v>100000</v>
       </c>
       <c r="D5" t="n">
-        <v>24000</v>
+        <v>25680</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+39.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -675,14 +675,14 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>24000</v>
+        <v>25680</v>
       </c>
       <c r="K5" t="n">
-        <v>-8000</v>
+        <v>10398</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-400.0%</t>
+          <t>+147.0%</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+969.3%</t>
+          <t>+430.9%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -782,11 +782,11 @@
         <v>73784.01000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-39098</v>
+        <v>-32100</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-288.7%</t>
+          <t>-329.9%</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -886,11 +886,11 @@
         <v>8136.3</v>
       </c>
       <c r="K9" t="n">
-        <v>16900</v>
+        <v>15800</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-48.5%</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+207.4%</t>
+          <t>+142.0%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1042,11 +1042,11 @@
         <v>46484</v>
       </c>
       <c r="K12" t="n">
-        <v>14398</v>
+        <v>19098</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+222.9%</t>
+          <t>+143.4%</t>
         </is>
       </c>
     </row>
@@ -1065,16 +1065,16 @@
         <v>100000</v>
       </c>
       <c r="D13" t="n">
-        <v>83420.75</v>
+        <v>93420.75</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+80.9%</t>
+          <t>+59.7%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1082,23 +1082,23 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-48.3%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>72820.75</v>
+        <v>82820.75</v>
       </c>
       <c r="K13" t="n">
-        <v>32252</v>
+        <v>36452</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+125.8%</t>
+          <t>+127.2%</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>20398</v>
+        <v>40398</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1214,47 +1214,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>许冰</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>150000</v>
+        <v>170000</v>
       </c>
       <c r="D16" t="n">
-        <v>35990</v>
+        <v>52796</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+76.7%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>35990</v>
+        <v>43996</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>59812</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-26.4%</t>
         </is>
       </c>
     </row>
@@ -1266,47 +1266,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>许冰</t>
+          <t>刘沁</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>170000</v>
+        <v>150000</v>
       </c>
       <c r="D17" t="n">
-        <v>52796</v>
+        <v>48276</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>+127.8%</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-63.9%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>50996</v>
+        <v>48276</v>
       </c>
       <c r="K17" t="n">
-        <v>59812</v>
+        <v>21194</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>+127.8%</t>
         </is>
       </c>
     </row>
@@ -1318,23 +1318,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>刘沁</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>150000</v>
       </c>
       <c r="D18" t="n">
-        <v>48276</v>
+        <v>50978</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+132.1%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1351,14 +1351,14 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>48276</v>
+        <v>50978</v>
       </c>
       <c r="K18" t="n">
-        <v>20796</v>
+        <v>0</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+132.1%</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
@@ -1474,23 +1474,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>马春兰</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="D21" t="n">
-        <v>398</v>
+        <v>21194</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-96.6%</t>
+          <t>+103.8%</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1507,14 +1507,14 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>398</v>
+        <v>21194</v>
       </c>
       <c r="K21" t="n">
-        <v>11592</v>
+        <v>10398</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-96.6%</t>
+          <t>+103.8%</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         <v>120000</v>
       </c>
       <c r="D22" t="n">
-        <v>20398</v>
+        <v>40796</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>+96.2%</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1559,14 +1559,14 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>20398</v>
+        <v>40796</v>
       </c>
       <c r="K22" t="n">
         <v>20796</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>+96.2%</t>
         </is>
       </c>
     </row>
@@ -1578,23 +1578,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>马春兰</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="D23" t="n">
-        <v>21194</v>
+        <v>20398</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+103.8%</t>
+          <t>+76.0%</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1611,14 +1611,14 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>21194</v>
+        <v>20398</v>
       </c>
       <c r="K23" t="n">
-        <v>10398</v>
+        <v>11592</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+103.8%</t>
+          <t>+76.0%</t>
         </is>
       </c>
     </row>
@@ -1659,18 +1659,18 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="J24" t="n">
         <v>42796</v>
       </c>
       <c r="K24" t="n">
-        <v>24800</v>
+        <v>18200</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+72.6%</t>
+          <t>+135.1%</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
         <v>1000</v>
       </c>
       <c r="K26" t="n">
-        <v>81794</v>
+        <v>82392</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1793,11 +1793,11 @@
         <v>48000</v>
       </c>
       <c r="D27" t="n">
-        <v>1796</v>
+        <v>2796</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1796</v>
+        <v>2796</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1845,16 +1845,16 @@
         <v>107400</v>
       </c>
       <c r="D28" t="n">
-        <v>14398</v>
+        <v>16398</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+200.2%</t>
+          <t>+215.7%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1871,14 +1871,14 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>14398</v>
+        <v>16398</v>
       </c>
       <c r="K28" t="n">
-        <v>4796</v>
+        <v>5194</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+200.2%</t>
+          <t>+215.7%</t>
         </is>
       </c>
     </row>
@@ -2202,18 +2202,18 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>300000</v>
       </c>
       <c r="D35" t="n">
-        <v>60625</v>
+        <v>63128</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>60625</v>
+        <v>63128</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2254,18 +2254,18 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>300000</v>
       </c>
       <c r="D36" t="n">
-        <v>63128</v>
+        <v>90625</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>63128</v>
+        <v>90625</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2306,18 +2306,18 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>韩雪</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>100000</v>
+        <v>400000</v>
       </c>
       <c r="D37" t="n">
-        <v>27998</v>
+        <v>182234</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>27998</v>
+        <v>182234</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2358,18 +2358,18 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>王凯</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>400000</v>
+        <v>50000</v>
       </c>
       <c r="D38" t="n">
-        <v>182234</v>
+        <v>24800</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>182234</v>
+        <v>24800</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2410,18 +2410,18 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>王凯</t>
+          <t>韩雪</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="D39" t="n">
-        <v>24800</v>
+        <v>58396</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>24800</v>
+        <v>58396</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2781,16 +2781,16 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>46986</v>
+        <v>47584</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+369.9%</t>
+          <t>+349.0%</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2807,14 +2807,14 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>46986</v>
+        <v>47584</v>
       </c>
       <c r="K46" t="n">
-        <v>10000</v>
+        <v>10598</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+369.9%</t>
+          <t>+349.0%</t>
         </is>
       </c>
     </row>
@@ -2937,16 +2937,16 @@
         <v>120000</v>
       </c>
       <c r="D49" t="n">
-        <v>19111.71</v>
+        <v>19453.87</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>734.6%</t>
+          <t>721.7%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2963,14 +2963,14 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>-121288.29</v>
+        <v>-120946.13</v>
       </c>
       <c r="K49" t="n">
-        <v>15398</v>
+        <v>15796</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-887.7%</t>
+          <t>-865.7%</t>
         </is>
       </c>
     </row>
@@ -2982,23 +2982,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>米兰兰</t>
+          <t>孙君兰</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>60000</v>
+        <v>130000</v>
       </c>
       <c r="D50" t="n">
-        <v>13700</v>
+        <v>35999.34</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+29.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3015,14 +3015,14 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>13700</v>
+        <v>35999.34</v>
       </c>
       <c r="K50" t="n">
-        <v>10600</v>
+        <v>35616</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+29.2%</t>
+          <t>+1.1%</t>
         </is>
       </c>
     </row>
@@ -3034,23 +3034,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>孙君兰</t>
+          <t>米兰兰</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>130000</v>
+        <v>60000</v>
       </c>
       <c r="D51" t="n">
-        <v>35759.34</v>
+        <v>18400</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+295.6%</t>
+          <t>+73.6%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3067,14 +3067,14 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>35759.34</v>
+        <v>18400</v>
       </c>
       <c r="K51" t="n">
-        <v>8796</v>
+        <v>10600</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+306.5%</t>
+          <t>+73.6%</t>
         </is>
       </c>
     </row>
@@ -3249,11 +3249,11 @@
         <v>204401</v>
       </c>
       <c r="D55" t="n">
-        <v>13564.98</v>
+        <v>14109.18</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3275,14 +3275,14 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>13564.98</v>
+        <v>14109.18</v>
       </c>
       <c r="K55" t="n">
         <v>18196</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-22.5%</t>
         </is>
       </c>
     </row>
@@ -3301,16 +3301,16 @@
         <v>259200</v>
       </c>
       <c r="D56" t="n">
-        <v>20210.64</v>
+        <v>20608.64</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+4370.9%</t>
+          <t>+4470.9%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3318,23 +3318,23 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+2915.1%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>8210.639999999999</v>
+        <v>8608.639999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>+1963.0%</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
@@ -3450,18 +3450,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>罗晗</t>
+          <t>陈新星</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>24000</v>
+        <v>134000</v>
       </c>
       <c r="D59" t="n">
-        <v>398</v>
+        <v>23000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3470,11 +3470,11 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>15218</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>398</v>
+        <v>7782</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -3502,18 +3502,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>陈新星</t>
+          <t>罗晗</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>134000</v>
+        <v>24000</v>
       </c>
       <c r="D60" t="n">
-        <v>23000</v>
+        <v>12398</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3522,11 +3522,11 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>15218</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>7782</v>
+        <v>12398</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -3606,23 +3606,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>王钰尧</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>50000</v>
+        <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>796</v>
+        <v>2490</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-84.2%</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3635,18 +3635,18 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>796</v>
+        <v>2490</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>3796</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-34.4%</t>
         </is>
       </c>
     </row>
@@ -3658,23 +3658,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>王钰尧</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>120000</v>
+        <v>50000</v>
       </c>
       <c r="D63" t="n">
-        <v>2490</v>
+        <v>1394</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-84.2%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3687,18 +3687,18 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>2490</v>
+        <v>1394</v>
       </c>
       <c r="K63" t="n">
-        <v>3796</v>
+        <v>0</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
@@ -3717,16 +3717,16 @@
         <v>120000</v>
       </c>
       <c r="D64" t="n">
-        <v>12992</v>
+        <v>20992</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>+2072.6%</t>
+          <t>+3410.4%</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3743,14 +3743,14 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>12992</v>
+        <v>20992</v>
       </c>
       <c r="K64" t="n">
         <v>-15602</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-183.3%</t>
+          <t>-234.5%</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>+89.8%</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -3798,11 +3798,11 @@
         <v>25808</v>
       </c>
       <c r="K65" t="n">
-        <v>13594</v>
+        <v>25594</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>+89.8%</t>
+          <t>+0.8%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>117784</v>
+        <v>118482</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>117784</v>
+        <v>118482</v>
       </c>
       <c r="K66" t="n">
-        <v>99396</v>
+        <v>99996</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-97.4%</t>
+          <t>-99.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -522,11 +522,11 @@
         <v>398</v>
       </c>
       <c r="K2" t="n">
-        <v>-75252</v>
+        <v>-35664</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-100.5%</t>
+          <t>-101.1%</t>
         </is>
       </c>
     </row>
@@ -597,16 +597,16 @@
         <v>280000</v>
       </c>
       <c r="D4" t="n">
-        <v>52990</v>
+        <v>53388</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>48990</v>
+        <v>49388</v>
       </c>
       <c r="K4" t="n">
-        <v>60996</v>
+        <v>70996</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-30.4%</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+39.6%</t>
+          <t>+36.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -678,11 +678,11 @@
         <v>25680</v>
       </c>
       <c r="K5" t="n">
-        <v>10398</v>
+        <v>10796</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+147.0%</t>
+          <t>+137.9%</t>
         </is>
       </c>
     </row>
@@ -753,16 +753,16 @@
         <v>73000</v>
       </c>
       <c r="D7" t="n">
-        <v>73784.01000000001</v>
+        <v>121064.01</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>101.1%</t>
+          <t>165.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+430.9%</t>
+          <t>+771.1%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -779,14 +779,14 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>73784.01000000001</v>
+        <v>121064.01</v>
       </c>
       <c r="K7" t="n">
         <v>-32100</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-329.9%</t>
+          <t>-477.1%</t>
         </is>
       </c>
     </row>
@@ -857,16 +857,16 @@
         <v>280000</v>
       </c>
       <c r="D9" t="n">
-        <v>8136.3</v>
+        <v>12116.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-63.6%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -883,14 +883,14 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8136.3</v>
+        <v>12116.3</v>
       </c>
       <c r="K9" t="n">
-        <v>15800</v>
+        <v>17400</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-30.4%</t>
         </is>
       </c>
     </row>
@@ -902,47 +902,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>苏怡意</t>
+          <t>姜玮</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>73000</v>
+        <v>50000</v>
       </c>
       <c r="D10" t="n">
-        <v>17598</v>
+        <v>16196</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-39.4%</t>
+          <t>+3868.8%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+60.6%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17598</v>
+        <v>8196</v>
       </c>
       <c r="K10" t="n">
-        <v>28694</v>
+        <v>-4582</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-38.7%</t>
+          <t>-278.9%</t>
         </is>
       </c>
     </row>
@@ -954,47 +954,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>苏怡意</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>50000</v>
+        <v>73000</v>
       </c>
       <c r="D11" t="n">
-        <v>16196</v>
+        <v>29798</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3868.8%</t>
+          <t>+3.2%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>+60.6%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8196</v>
+        <v>29798</v>
       </c>
       <c r="K11" t="n">
-        <v>-4582</v>
+        <v>28694</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-278.9%</t>
+          <t>+3.8%</t>
         </is>
       </c>
     </row>
@@ -1065,40 +1065,40 @@
         <v>100000</v>
       </c>
       <c r="D13" t="n">
-        <v>93420.75</v>
+        <v>103420.75</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>103.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+59.7%</t>
+          <t>+50.8%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>10600</v>
+        <v>15580</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>82820.75</v>
+        <v>87840.75</v>
       </c>
       <c r="K13" t="n">
-        <v>36452</v>
+        <v>46452</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+127.2%</t>
+          <t>+89.1%</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-34.9%</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1198,11 +1198,11 @@
         <v>10796</v>
       </c>
       <c r="K15" t="n">
-        <v>15796.01</v>
+        <v>16592.01</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-34.9%</t>
         </is>
       </c>
     </row>
@@ -1214,47 +1214,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>许冰</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>170000</v>
+        <v>150000</v>
       </c>
       <c r="D16" t="n">
-        <v>52796</v>
+        <v>51376</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>8800</v>
+        <v>0</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+76.7%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>43996</v>
+        <v>51376</v>
       </c>
       <c r="K16" t="n">
-        <v>59812</v>
+        <v>0</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
@@ -1273,16 +1273,16 @@
         <v>150000</v>
       </c>
       <c r="D17" t="n">
-        <v>48276</v>
+        <v>58674</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+127.8%</t>
+          <t>+176.8%</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1299,14 +1299,14 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>48276</v>
+        <v>58674</v>
       </c>
       <c r="K17" t="n">
         <v>21194</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+127.8%</t>
+          <t>+176.8%</t>
         </is>
       </c>
     </row>
@@ -1318,47 +1318,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>许冰</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>150000</v>
+        <v>170000</v>
       </c>
       <c r="D18" t="n">
-        <v>50978</v>
+        <v>71194</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+6.9%</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+76.7%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>50978</v>
+        <v>62394</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>61612</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+1.3%</t>
         </is>
       </c>
     </row>
@@ -1481,16 +1481,16 @@
         <v>80000</v>
       </c>
       <c r="D21" t="n">
-        <v>21194</v>
+        <v>21990</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+103.8%</t>
+          <t>+111.5%</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1507,14 +1507,14 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>21194</v>
+        <v>21990</v>
       </c>
       <c r="K21" t="n">
         <v>10398</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+103.8%</t>
+          <t>+111.5%</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+96.2%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1562,11 +1562,11 @@
         <v>40796</v>
       </c>
       <c r="K22" t="n">
-        <v>20796</v>
+        <v>47616</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+96.2%</t>
+          <t>-14.3%</t>
         </is>
       </c>
     </row>
@@ -1585,16 +1585,16 @@
         <v>40000</v>
       </c>
       <c r="D23" t="n">
-        <v>20398</v>
+        <v>26998</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+76.0%</t>
+          <t>+132.9%</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1611,14 +1611,14 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>20398</v>
+        <v>26998</v>
       </c>
       <c r="K23" t="n">
         <v>11592</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+76.0%</t>
+          <t>+132.9%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+72.6%</t>
+          <t>+69.8%</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1666,11 +1666,11 @@
         <v>42796</v>
       </c>
       <c r="K24" t="n">
-        <v>18200</v>
+        <v>18598</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+135.1%</t>
+          <t>+130.1%</t>
         </is>
       </c>
     </row>
@@ -1741,16 +1741,16 @@
         <v>210000</v>
       </c>
       <c r="D26" t="n">
-        <v>1000</v>
+        <v>4680</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-99.1%</t>
+          <t>-95.6%</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1767,14 +1767,14 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1000</v>
+        <v>4680</v>
       </c>
       <c r="K26" t="n">
         <v>82392</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-98.8%</t>
+          <t>-94.3%</t>
         </is>
       </c>
     </row>
@@ -1897,16 +1897,16 @@
         <v>120000</v>
       </c>
       <c r="D29" t="n">
-        <v>18392</v>
+        <v>28392</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+19.4%</t>
+          <t>+11.8%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1923,14 +1923,14 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>18392</v>
+        <v>28392</v>
       </c>
       <c r="K29" t="n">
-        <v>10398</v>
+        <v>20398</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+76.9%</t>
+          <t>+39.2%</t>
         </is>
       </c>
     </row>
@@ -2046,18 +2046,18 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>唐晟</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>50000</v>
+        <v>300000</v>
       </c>
       <c r="D32" t="n">
-        <v>9000</v>
+        <v>55823</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>9000</v>
+        <v>55823</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2098,18 +2098,18 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>唐晟</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>300000</v>
+        <v>50000</v>
       </c>
       <c r="D33" t="n">
-        <v>55823</v>
+        <v>9398</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>55823</v>
+        <v>9398</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2157,11 +2157,11 @@
         <v>250000</v>
       </c>
       <c r="D34" t="n">
-        <v>47021</v>
+        <v>47287</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>47021</v>
+        <v>47287</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2209,11 +2209,11 @@
         <v>300000</v>
       </c>
       <c r="D35" t="n">
-        <v>63128</v>
+        <v>64126</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>63128</v>
+        <v>64126</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2261,11 +2261,11 @@
         <v>300000</v>
       </c>
       <c r="D36" t="n">
-        <v>90625</v>
+        <v>100625</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>90625</v>
+        <v>100625</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2729,16 +2729,16 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>32900</v>
+        <v>42900</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+2412.6%</t>
+          <t>+4925.1%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2755,14 +2755,14 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>32900</v>
+        <v>42900</v>
       </c>
       <c r="K45" t="n">
         <v>-9012</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-465.1%</t>
+          <t>-576.0%</t>
         </is>
       </c>
     </row>
@@ -2781,16 +2781,16 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>47584</v>
+        <v>55584</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+349.0%</t>
+          <t>+424.5%</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2807,14 +2807,14 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>47584</v>
+        <v>55584</v>
       </c>
       <c r="K46" t="n">
         <v>10598</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+349.0%</t>
+          <t>+424.5%</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3018,11 +3018,11 @@
         <v>35999.34</v>
       </c>
       <c r="K50" t="n">
-        <v>35616</v>
+        <v>36014</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-0.0%</t>
         </is>
       </c>
     </row>
@@ -3034,31 +3034,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>米兰兰</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="D51" t="n">
-        <v>18400</v>
+        <v>40600</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+73.6%</t>
+          <t>-44.9%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3067,14 +3067,14 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>18400</v>
+        <v>37900</v>
       </c>
       <c r="K51" t="n">
-        <v>10600</v>
+        <v>70100</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+73.6%</t>
+          <t>-45.9%</t>
         </is>
       </c>
     </row>
@@ -3086,31 +3086,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>米兰兰</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="D52" t="n">
-        <v>40600</v>
+        <v>25900</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-42.4%</t>
+          <t>+43.1%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3119,14 +3119,14 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>37900</v>
+        <v>25900</v>
       </c>
       <c r="K52" t="n">
-        <v>67000</v>
+        <v>18100</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-43.4%</t>
+          <t>+43.1%</t>
         </is>
       </c>
     </row>
@@ -3249,11 +3249,11 @@
         <v>204401</v>
       </c>
       <c r="D55" t="n">
-        <v>14109.18</v>
+        <v>15940.22</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3275,14 +3275,14 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>14109.18</v>
+        <v>15940.22</v>
       </c>
       <c r="K55" t="n">
         <v>18196</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-12.4%</t>
         </is>
       </c>
     </row>
@@ -3301,16 +3301,16 @@
         <v>259200</v>
       </c>
       <c r="D56" t="n">
-        <v>20608.64</v>
+        <v>31326.08</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+4470.9%</t>
+          <t>+130.6%</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3327,14 +3327,14 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>8608.639999999999</v>
+        <v>19326.08</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+61.1%</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>+36.6%</t>
+          <t>+29.0%</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3382,11 +3382,11 @@
         <v>62701</v>
       </c>
       <c r="K57" t="n">
-        <v>40994</v>
+        <v>43394</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>+53.0%</t>
+          <t>+44.5%</t>
         </is>
       </c>
     </row>
@@ -3613,16 +3613,16 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>2490</v>
+        <v>2888</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-84.2%</t>
+          <t>-81.7%</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3639,14 +3639,14 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>2490</v>
+        <v>2888</v>
       </c>
       <c r="K62" t="n">
         <v>3796</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-23.9%</t>
         </is>
       </c>
     </row>
@@ -3769,24 +3769,24 @@
         <v>120000</v>
       </c>
       <c r="D65" t="n">
-        <v>25808</v>
+        <v>32206</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>+25.8%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3795,14 +3795,14 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>25808</v>
+        <v>22006</v>
       </c>
       <c r="K65" t="n">
         <v>25594</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-14.0%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>118482</v>
+        <v>119530</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>+15.0%</t>
+          <t>+10.7%</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -3847,14 +3847,14 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>118482</v>
+        <v>119530</v>
       </c>
       <c r="K66" t="n">
-        <v>99996</v>
+        <v>104996</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>+18.5%</t>
+          <t>+13.8%</t>
         </is>
       </c>
     </row>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -854,14 +854,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>280000</v>
+        <v>150000</v>
       </c>
       <c r="D9" t="n">
         <v>12116.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -906,14 +906,14 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>50000</v>
+        <v>130000</v>
       </c>
       <c r="D10" t="n">
         <v>16196</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -958,14 +958,14 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>73000</v>
+        <v>160000</v>
       </c>
       <c r="D11" t="n">
         <v>29798</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1006,47 +1006,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>120000</v>
+        <v>270000</v>
       </c>
       <c r="D12" t="n">
-        <v>53484</v>
+        <v>103420.75</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+142.0%</t>
+          <t>+50.8%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>7000</v>
+        <v>15580</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+133.3%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>46484</v>
+        <v>87840.75</v>
       </c>
       <c r="K12" t="n">
-        <v>19098</v>
+        <v>46452</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+143.4%</t>
+          <t>+89.1%</t>
         </is>
       </c>
     </row>
@@ -1058,47 +1058,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>李明</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D13" t="n">
-        <v>103420.75</v>
+        <v>53484</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>103.4%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+50.8%</t>
+          <t>+142.0%</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>15580</v>
+        <v>7000</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>+133.3%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>87840.75</v>
+        <v>46484</v>
       </c>
       <c r="K13" t="n">
-        <v>46452</v>
+        <v>19098</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+89.1%</t>
+          <t>+143.4%</t>
         </is>
       </c>
     </row>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -1379,23 +1379,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D29" t="n">
-        <v>25680</v>
+        <v>31032</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,29 +1407,29 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>25680</v>
+        <v>31032</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>陈翔宇</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="D30" t="n">
-        <v>50900</v>
+        <v>25680</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,63 +1441,63 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>50900</v>
+        <v>25680</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>陈月娇</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="D31" t="n">
-        <v>28990</v>
+        <v>50900</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>24800</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4190</v>
+        <v>50900</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="D32" t="n">
-        <v>55408.64</v>
+        <v>48394</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,41 +1509,41 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>55408.64</v>
+        <v>48394</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>陈月娇</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>2888</v>
+        <v>28990</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2888</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="34">
@@ -1554,18 +1554,18 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>唐晟</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>50000</v>
+        <v>250000</v>
       </c>
       <c r="D34" t="n">
-        <v>9796</v>
+        <v>55408.64</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,29 +1577,29 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9796</v>
+        <v>55408.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>38558</v>
+        <v>2888</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>38558</v>
+        <v>2888</v>
       </c>
     </row>
     <row r="36">
@@ -1622,18 +1622,18 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>唐晟</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>250000</v>
+        <v>50000</v>
       </c>
       <c r="D36" t="n">
-        <v>48107.5</v>
+        <v>9796</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>48107.5</v>
+        <v>9796</v>
       </c>
     </row>
     <row r="37">
@@ -1656,18 +1656,18 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="D37" t="n">
-        <v>57423</v>
+        <v>38558</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,63 +1679,63 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>57423</v>
+        <v>38558</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>280000</v>
+        <v>250000</v>
       </c>
       <c r="D38" t="n">
-        <v>53388</v>
+        <v>48107.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>49388</v>
+        <v>48107.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>334800</v>
+        <v>300000</v>
       </c>
       <c r="D39" t="n">
-        <v>62701</v>
+        <v>57423</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,63 +1747,63 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>62701</v>
+        <v>57423</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>苏怡意</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>160000</v>
+        <v>280000</v>
       </c>
       <c r="D40" t="n">
-        <v>29798</v>
+        <v>53388</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>29798</v>
+        <v>49388</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>邓璐</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>120000</v>
+        <v>334800</v>
       </c>
       <c r="D41" t="n">
-        <v>20992</v>
+        <v>62701</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,63 +1815,63 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>20992</v>
+        <v>62701</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>陈新星</t>
+          <t>苏怡意</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>134000</v>
+        <v>160000</v>
       </c>
       <c r="D42" t="n">
-        <v>23000</v>
+        <v>29798</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>15218</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>7782</v>
+        <v>29798</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>73000</v>
+        <v>120000</v>
       </c>
       <c r="D43" t="n">
-        <v>121462.01</v>
+        <v>20992</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>166.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,63 +1883,63 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>121462.01</v>
+        <v>20992</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>陈紫灵</t>
+          <t>陈新星</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>120000</v>
+        <v>134000</v>
       </c>
       <c r="D44" t="n">
-        <v>19453.87</v>
+        <v>23000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>140400</v>
+        <v>15218</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>721.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>-120946.13</v>
+        <v>7782</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>杨红瑞</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>107400</v>
+        <v>73000</v>
       </c>
       <c r="D45" t="n">
-        <v>16398</v>
+        <v>121462.01</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>166.4%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,97 +1951,97 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>16398</v>
+        <v>121462.01</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>陈紫灵</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>210000</v>
+        <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>29480</v>
+        <v>19453.87</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>140400</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>721.7%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>29480</v>
+        <v>-120946.13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>杨红瑞</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>130000</v>
+        <v>107400</v>
       </c>
       <c r="D47" t="n">
-        <v>16594</v>
+        <v>16398</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8594</v>
+        <v>16398</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>田奇</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>150000</v>
+        <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>18804.3</v>
+        <v>29480</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,63 +2053,63 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>18804.3</v>
+        <v>29480</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周思若</t>
+          <t>姜玮</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>259200</v>
+        <v>130000</v>
       </c>
       <c r="D49" t="n">
-        <v>31526.08</v>
+        <v>16594</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>12200</v>
+        <v>8000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>19326.08</v>
+        <v>8594</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>谌黎平</t>
+          <t>田奇</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>40000</v>
+        <v>150000</v>
       </c>
       <c r="D50" t="n">
-        <v>42796</v>
+        <v>18804.3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,41 +2121,41 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>42796</v>
+        <v>18804.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>周思若</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>120000</v>
+        <v>259200</v>
       </c>
       <c r="D51" t="n">
-        <v>1598</v>
+        <v>31526.08</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>6600</v>
+        <v>12200</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>413.0%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>-5002</v>
+        <v>19326.08</v>
       </c>
     </row>
     <row r="52">
@@ -2166,18 +2166,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>李颜君</t>
+          <t>谌黎平</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>40000</v>
       </c>
       <c r="D52" t="n">
-        <v>398</v>
+        <v>42796</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>398</v>
+        <v>42796</v>
       </c>
     </row>
     <row r="53">
@@ -2200,52 +2200,52 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>余婉丽</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>50000</v>
+        <v>120000</v>
       </c>
       <c r="D53" t="n">
-        <v>398</v>
+        <v>1598</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>413.0%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>398</v>
+        <v>-5002</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>林峻民</t>
+          <t>李颜君</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>32000</v>
+        <v>40000</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,29 +2257,29 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>胡梦莉</t>
+          <t>余婉丽</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>50000</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>李家慧</t>
+          <t>林峻民</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>50000</v>
+        <v>32000</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2331,16 +2331,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>吴静文</t>
+          <t>胡梦莉</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2365,16 +2365,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>王芊雅</t>
+          <t>李家慧</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2399,16 +2399,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>黄雅琴</t>
+          <t>吴静文</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2433,16 +2433,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>沈月</t>
+          <t>王芊雅</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -466,52 +466,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>田婉丽</t>
+          <t>陈新星</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>100000</v>
+        <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>91384</v>
+        <v>23000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>15218</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>91384</v>
+        <v>7782</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>王秋</t>
+          <t>田婉丽</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>81474</v>
+        <v>91384</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,29 +523,29 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>81474</v>
+        <v>91384</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>朱锋剑</t>
+          <t>罗晗</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>90000</v>
+        <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>8000</v>
+        <v>14078</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,63 +557,63 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8000</v>
+        <v>14078</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>马雅丽</t>
+          <t>林峻民</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>204401</v>
+        <v>32000</v>
       </c>
       <c r="D5" t="n">
-        <v>16708.32</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>412</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>16296.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>白蕾</t>
+          <t>朱锋剑</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>150000</v>
+        <v>90000</v>
       </c>
       <c r="D6" t="n">
-        <v>11194</v>
+        <v>8000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,131 +625,131 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11194</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>尹欢</t>
+          <t>孙君兰</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>120000</v>
+        <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>8398</v>
+        <v>36319.34</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8398</v>
+        <v>35999.34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40000</v>
+        <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>26998</v>
+        <v>40600</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>26998</v>
+        <v>37900</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>陈紫灵</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>300000</v>
+        <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>195876</v>
+        <v>19453.87</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>140400</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>721.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>195876</v>
+        <v>-120946.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>罗晗</t>
+          <t>米兰兰</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24000</v>
+        <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>14078</v>
+        <v>25900</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,29 +761,29 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>14078</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>韩雪</t>
+          <t>胡梦莉</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="D11" t="n">
-        <v>58396.00000000001</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,29 +795,29 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>58396.00000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>普元媛</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>48000</v>
+        <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>2796</v>
+        <v>107499</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2796</v>
+        <v>107499</v>
       </c>
     </row>
     <row r="13">
@@ -840,18 +840,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>王凯</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>50000</v>
+        <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>24800</v>
+        <v>57423</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>24800</v>
+        <v>57423</v>
       </c>
     </row>
     <row r="14">
@@ -903,23 +903,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>米兰兰</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>60000</v>
+        <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>25900</v>
+        <v>55408.64</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,63 +931,63 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>25900</v>
+        <v>55408.64</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>许冰</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>170000</v>
+        <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>71194</v>
+        <v>48107.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>8800</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>62394</v>
+        <v>48107.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>刘沁</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>60354</v>
+        <v>195876</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,97 +999,97 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>60354</v>
+        <v>195876</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>唐晟</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>120000</v>
+        <v>50000</v>
       </c>
       <c r="D18" t="n">
-        <v>48086</v>
+        <v>9796</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>35086</v>
+        <v>9796</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>270000</v>
+        <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>103818.75</v>
+        <v>38558</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>15580</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88238.75</v>
+        <v>38558</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>王凯</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>120000</v>
+        <v>50000</v>
       </c>
       <c r="D20" t="n">
-        <v>45796</v>
+        <v>24800</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>45796</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="21">
@@ -1112,18 +1112,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>韩雪</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="D21" t="n">
-        <v>107499</v>
+        <v>58396.00000000001</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,29 +1135,29 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>107499</v>
+        <v>58396.00000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>陈翔宇</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="D22" t="n">
-        <v>51376</v>
+        <v>25680</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,233 +1169,233 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>51376</v>
+        <v>25680</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>120000</v>
+        <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>40600</v>
+        <v>53388</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2700</v>
+        <v>4000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>37900</v>
+        <v>49388</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>陈舒羽</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>56784</v>
+        <v>398</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1658.3%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>56784</v>
+        <v>-6202</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>孙君兰</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>130000</v>
+        <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>36319.34</v>
+        <v>121462.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>166.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>35999.34</v>
+        <v>121462.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>马春兰</t>
+          <t>余婉丽</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>80000</v>
+        <v>50000</v>
       </c>
       <c r="D26" t="n">
-        <v>21592</v>
+        <v>398</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19912</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>朱碧丹</t>
+          <t>王秋</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>120000</v>
+        <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>32206</v>
+        <v>81474</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>10200</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>22006</v>
+        <v>81474</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>王钰尧</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>50000</v>
+        <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>13394</v>
+        <v>103818.75</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>15580</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>13394</v>
+        <v>88238.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>沈悦</t>
+          <t>田奇</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>31032</v>
+        <v>18804.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,63 +1407,63 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>31032</v>
+        <v>18804.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>李明</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>25680</v>
+        <v>48086</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>25680</v>
+        <v>35086</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>苏怡意</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>200000</v>
+        <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>50900</v>
+        <v>29798</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,97 +1475,97 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>50900</v>
+        <v>29798</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>姜玮</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>200000</v>
+        <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>48394</v>
+        <v>16594</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>48394</v>
+        <v>8594</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>陈月娇</t>
+          <t>李家慧</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>120000</v>
+        <v>50000</v>
       </c>
       <c r="D33" t="n">
-        <v>28990</v>
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>24800</v>
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>250000</v>
+        <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>55408.64</v>
+        <v>45796</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,29 +1577,29 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>55408.64</v>
+        <v>45796</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>李颜君</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>2888</v>
+        <v>398</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,29 +1611,29 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2888</v>
+        <v>398</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>唐晟</t>
+          <t>谌黎平</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>9796</v>
+        <v>42796</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,63 +1645,63 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>9796</v>
+        <v>42796</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>马春兰</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="D37" t="n">
-        <v>38558</v>
+        <v>21592</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>38558</v>
+        <v>19912</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>250000</v>
+        <v>40000</v>
       </c>
       <c r="D38" t="n">
-        <v>48107.5</v>
+        <v>26998</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,29 +1713,29 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>48107.5</v>
+        <v>26998</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>吴静文</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>57423</v>
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,63 +1747,63 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>57423</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>许冰</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>280000</v>
+        <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>53388</v>
+        <v>71194</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4000</v>
+        <v>8800</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>49388</v>
+        <v>62394</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>白蕾</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>334800</v>
+        <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>62701</v>
+        <v>11194</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,29 +1815,29 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>62701</v>
+        <v>11194</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>苏怡意</t>
+          <t>王芊雅</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="D42" t="n">
-        <v>29798</v>
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1849,29 +1849,29 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>29798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>刘沁</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="D43" t="n">
-        <v>20992</v>
+        <v>60354</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,63 +1883,63 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>20992</v>
+        <v>60354</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>陈新星</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>134000</v>
+        <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>23000</v>
+        <v>51376</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>15218</v>
+        <v>0</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>7782</v>
+        <v>51376</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>73000</v>
+        <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>121462.01</v>
+        <v>48394</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>166.4%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,63 +1951,63 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>121462.01</v>
+        <v>48394</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>陈紫灵</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>19453.87</v>
+        <v>50900</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>140400</v>
+        <v>0</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>721.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>-120946.13</v>
+        <v>50900</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>杨红瑞</t>
+          <t>陈舒羽</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>107400</v>
+        <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>16398</v>
+        <v>56784</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,29 +2019,29 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>16398</v>
+        <v>56784</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>210000</v>
+        <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>29480</v>
+        <v>31032</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,63 +2053,63 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>29480</v>
+        <v>31032</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>尹欢</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>130000</v>
+        <v>120000</v>
       </c>
       <c r="D49" t="n">
-        <v>16594</v>
+        <v>8398</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>8594</v>
+        <v>8398</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>田奇</t>
+          <t>庄鑫</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>150000</v>
+        <v>40000</v>
       </c>
       <c r="D50" t="n">
-        <v>18804.3</v>
+        <v>0</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,131 +2121,131 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>18804.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周思若</t>
+          <t>张回</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>259200</v>
+        <v>10000</v>
       </c>
       <c r="D51" t="n">
-        <v>31526.08</v>
+        <v>0</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>12200</v>
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>19326.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>谌黎平</t>
+          <t>陈月娇</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>40000</v>
+        <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>42796</v>
+        <v>28990</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>42796</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>120000</v>
+        <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>1598</v>
+        <v>29480</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>413.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>-5002</v>
+        <v>29480</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>李颜君</t>
+          <t>杨红瑞</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>40000</v>
+        <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>398</v>
+        <v>16398</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,29 +2257,29 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>398</v>
+        <v>16398</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>余婉丽</t>
+          <t>普元媛</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>50000</v>
+        <v>48000</v>
       </c>
       <c r="D55" t="n">
-        <v>398</v>
+        <v>2796</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>398</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>林峻民</t>
+          <t>马奇君</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>32000</v>
+        <v>20000</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2331,23 +2331,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>胡梦莉</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>50000</v>
+        <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>2888</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,29 +2359,29 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>2888</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>李家慧</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>50000</v>
+        <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>20992</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,63 +2393,63 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>20992</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>吴静文</t>
+          <t>朱碧丹</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>32206</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>22006</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>王芊雅</t>
+          <t>王钰尧</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>13394</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,29 +2461,29 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>13394</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>庄鑫</t>
+          <t>邓璐</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>40000</v>
+        <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>62701</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,75 +2495,75 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>62701</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>张回</t>
+          <t>马雅丽</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>10000</v>
+        <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>16708.32</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>16296.32</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>马奇君</t>
+          <t>周思若</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>20000</v>
+        <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>31526.08</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>12200</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>19326.08</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,23 +473,23 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>15218</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>7782</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>91384</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>91384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>14078</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -609,11 +609,11 @@
         <v>90000</v>
       </c>
       <c r="D6" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>36319.34</v>
+        <v>1523.34</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -655,11 +655,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>35999.34</v>
+        <v>1203.34</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>40600</v>
+        <v>2000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>37900</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>19453.87</v>
+        <v>861.87</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>140400</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>721.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-120946.13</v>
+        <v>861.87</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>25900</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -847,11 +847,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>57423</v>
+        <v>67423</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>57423</v>
+        <v>67423</v>
       </c>
     </row>
     <row r="14">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>48107.5</v>
+        <v>47709.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>48107.5</v>
+        <v>47709.5</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>195876</v>
+        <v>175478</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>195876</v>
+        <v>175478</v>
       </c>
     </row>
     <row r="18">
@@ -1051,11 +1051,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>38558</v>
+        <v>13160</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>38558</v>
+        <v>13160</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>50000</v>
       </c>
       <c r="D20" t="n">
-        <v>24800</v>
+        <v>0</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>24800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1153,11 +1153,11 @@
         <v>100000</v>
       </c>
       <c r="D22" t="n">
-        <v>25680</v>
+        <v>0</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>25680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1187,23 +1187,23 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>53388</v>
+        <v>0</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>49388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1221,23 +1221,23 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1658.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>-6202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>121462.01</v>
+        <v>0</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>166.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>121462.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>50000</v>
       </c>
       <c r="D26" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>81474</v>
+        <v>0</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>81474</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1357,23 +1357,23 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>103818.75</v>
+        <v>4169.75</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>15580</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>88238.75</v>
+        <v>4169.75</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>18804.3</v>
+        <v>924.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>18804.3</v>
+        <v>924.3</v>
       </c>
     </row>
     <row r="30">
@@ -1425,23 +1425,23 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>48086</v>
+        <v>0</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>35086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>29798</v>
+        <v>200</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>29798</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -1493,23 +1493,23 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>16594</v>
+        <v>400</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>8594</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33">
@@ -1561,11 +1561,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>45796</v>
+        <v>0</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>45796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>42796</v>
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>42796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1663,23 +1663,23 @@
         <v>80000</v>
       </c>
       <c r="D37" t="n">
-        <v>21592</v>
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>19912</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1697,11 +1697,11 @@
         <v>40000</v>
       </c>
       <c r="D38" t="n">
-        <v>26998</v>
+        <v>0</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>26998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1765,23 +1765,23 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>71194</v>
+        <v>0</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>8800</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>62394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>11194</v>
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>11194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1867,11 +1867,11 @@
         <v>150000</v>
       </c>
       <c r="D43" t="n">
-        <v>60354</v>
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>60354</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>51376</v>
+        <v>0</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>51376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>48394</v>
+        <v>0</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>48394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>50900</v>
+        <v>22900</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>50900</v>
+        <v>22900</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>56784</v>
+        <v>0</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>56784</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>31032</v>
+        <v>0</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>31032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>120000</v>
       </c>
       <c r="D49" t="n">
-        <v>8398</v>
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>8398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2173,23 +2173,23 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>28990</v>
+        <v>0</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>24800</v>
+        <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>4190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>29480</v>
+        <v>0</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>29480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>16398</v>
+        <v>0</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>16398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>48000</v>
       </c>
       <c r="D55" t="n">
-        <v>2796</v>
+        <v>0</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>2796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2343,11 +2343,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>2888</v>
+        <v>0</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>2888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>20992</v>
+        <v>0</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>20992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2411,23 +2411,23 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>32206</v>
+        <v>0</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>10200</v>
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>22006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>13394</v>
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>13394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>62701</v>
+        <v>6711.000000000001</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>62701</v>
+        <v>6711.000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>16708.32</v>
+        <v>7114.32</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>16296.32</v>
+        <v>6702.32</v>
       </c>
     </row>
     <row r="63">
@@ -2547,23 +2547,23 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>31526.08</v>
+        <v>2936.08</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>12200</v>
+        <v>200</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>19326.08</v>
+        <v>2736.08</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,23 +473,23 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>15218</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>7782</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>91384</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>91384</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>14078</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>14078</v>
       </c>
     </row>
     <row r="5">
@@ -609,11 +609,11 @@
         <v>90000</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>1523.34</v>
+        <v>36717.34</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -655,11 +655,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1203.34</v>
+        <v>36397.34</v>
       </c>
     </row>
     <row r="8">
@@ -677,23 +677,23 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>2000</v>
+        <v>40600</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2000</v>
+        <v>37900</v>
       </c>
     </row>
     <row r="9">
@@ -711,23 +711,23 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>861.87</v>
+        <v>19453.87</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>140400</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>721.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>861.87</v>
+        <v>-120946.13</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>25900</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="11">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>47709.5</v>
+        <v>48107.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>47709.5</v>
+        <v>48107.5</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>175478</v>
+        <v>195876</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>175478</v>
+        <v>195876</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>50000</v>
       </c>
       <c r="D18" t="n">
-        <v>9796</v>
+        <v>10194</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>9796</v>
+        <v>10194</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>13160</v>
+        <v>38558</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>13160</v>
+        <v>38558</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>50000</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="21">
@@ -1153,11 +1153,11 @@
         <v>100000</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>28080</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>28080</v>
       </c>
     </row>
     <row r="23">
@@ -1187,23 +1187,23 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>99386</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>95386</v>
       </c>
     </row>
     <row r="24">
@@ -1221,23 +1221,23 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1658.3%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>-6202</v>
       </c>
     </row>
     <row r="25">
@@ -1255,23 +1255,23 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>121462.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>166.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>115062.01</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>50000</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27">
@@ -1323,23 +1323,23 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>81474</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>73474</v>
       </c>
     </row>
     <row r="28">
@@ -1357,23 +1357,23 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>4169.75</v>
+        <v>125939.75</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>38380</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4169.75</v>
+        <v>87559.75</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>924.3</v>
+        <v>18804.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>924.3</v>
+        <v>18804.3</v>
       </c>
     </row>
     <row r="30">
@@ -1425,23 +1425,23 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>57984</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>44984</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>200</v>
+        <v>29798</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>200</v>
+        <v>29798</v>
       </c>
     </row>
     <row r="32">
@@ -1493,23 +1493,23 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>400</v>
+        <v>16594</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>400</v>
+        <v>8594</v>
       </c>
     </row>
     <row r="33">
@@ -1561,11 +1561,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>56194</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>56194</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>42796</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>42796</v>
       </c>
     </row>
     <row r="37">
@@ -1663,23 +1663,23 @@
         <v>80000</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>21592</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>19912</v>
       </c>
     </row>
     <row r="38">
@@ -1697,11 +1697,11 @@
         <v>40000</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>26998</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>26998</v>
       </c>
     </row>
     <row r="39">
@@ -1765,23 +1765,23 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>71194</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>62394</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>12394</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>12394</v>
       </c>
     </row>
     <row r="42">
@@ -1867,11 +1867,11 @@
         <v>150000</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>73554</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>73554</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>53056</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>53056</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>48394</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>48394</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>22900</v>
+        <v>60900</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>22900</v>
+        <v>60900</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>56784</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>56784</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>31032</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>31032</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>120000</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>8398</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>8398</v>
       </c>
     </row>
     <row r="50">
@@ -2173,23 +2173,23 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>28990</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>55878</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>55878</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>24398</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>24398</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>48000</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>2796</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="56">
@@ -2343,11 +2343,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>2888</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>2888</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>25190</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>25190</v>
       </c>
     </row>
     <row r="59">
@@ -2411,23 +2411,23 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>32206</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>22006</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>13394</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>13394</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>6711.000000000001</v>
+        <v>71099</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6711.000000000001</v>
+        <v>71099</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>7114.32</v>
+        <v>17106.32</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>6702.32</v>
+        <v>16694.32</v>
       </c>
     </row>
     <row r="63">
@@ -2547,23 +2547,23 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>2936.08</v>
+        <v>31526.08</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>200</v>
+        <v>12200</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2736.08</v>
+        <v>19326.08</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -507,11 +507,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>91384</v>
+        <v>93064</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>91384</v>
+        <v>93064</v>
       </c>
     </row>
     <row r="4">
@@ -575,11 +575,11 @@
         <v>32000</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6">
@@ -677,11 +677,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>40600</v>
+        <v>63600</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>37900</v>
+        <v>60900</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>19453.87</v>
+        <v>37851.87</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>721.7%</t>
+          <t>370.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-120946.13</v>
+        <v>-102548.13</v>
       </c>
     </row>
     <row r="10">
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>99386</v>
+        <v>105986</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>95386</v>
+        <v>101986</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>398</v>
+        <v>5398</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1658.3%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>-6202</v>
+        <v>-1202</v>
       </c>
     </row>
     <row r="25">
@@ -1263,15 +1263,15 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6400</v>
+        <v>22400</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>115062.01</v>
+        <v>99062.01000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>125939.75</v>
+        <v>126939.75</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>87559.75</v>
+        <v>88559.75</v>
       </c>
     </row>
     <row r="29">
@@ -1493,11 +1493,11 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>16594</v>
+        <v>16992</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>8594</v>
+        <v>8992</v>
       </c>
     </row>
     <row r="33">
@@ -1765,11 +1765,11 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>71194</v>
+        <v>116794</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>62394</v>
+        <v>107994</v>
       </c>
     </row>
     <row r="41">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>25200</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>-25200</v>
       </c>
     </row>
     <row r="43">
@@ -1935,11 +1935,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>48394</v>
+        <v>48894</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>48394</v>
+        <v>48894</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>60900</v>
+        <v>70900</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>60900</v>
+        <v>70900</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>56784</v>
+        <v>57382</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>56784</v>
+        <v>57382</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>31032</v>
+        <v>49430</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>31032</v>
+        <v>49430</v>
       </c>
     </row>
     <row r="49">
@@ -2079,15 +2079,15 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>8398</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="50">
@@ -2207,11 +2207,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>55878</v>
+        <v>66276</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>55878</v>
+        <v>66276</v>
       </c>
     </row>
     <row r="54">
@@ -2513,11 +2513,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>17106.32</v>
+        <v>17504.32</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>16694.32</v>
+        <v>17092.32</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>31526.08</v>
+        <v>40322.08</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>19326.08</v>
+        <v>28122.08</v>
       </c>
     </row>
     <row r="64">
@@ -2581,11 +2581,11 @@
         <v>20796</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="65">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>23000</v>
+        <v>23398</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>7782</v>
+        <v>8180</v>
       </c>
     </row>
     <row r="3">
@@ -575,11 +575,11 @@
         <v>32000</v>
       </c>
       <c r="D5" t="n">
-        <v>398</v>
+        <v>2388</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>398</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="6">
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>36717.34</v>
+        <v>37115.34</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>36397.34</v>
+        <v>36795.34</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>63600</v>
+        <v>71100</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>60900</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="9">
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>105986</v>
+        <v>121986</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>101986</v>
+        <v>117986</v>
       </c>
     </row>
     <row r="24">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>126939.75</v>
+        <v>127337.75</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>88559.75</v>
+        <v>88957.75</v>
       </c>
     </row>
     <row r="29">
@@ -1425,11 +1425,11 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>57984</v>
+        <v>65484</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>44984</v>
+        <v>52484</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>29798</v>
+        <v>30196</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>29798</v>
+        <v>30196</v>
       </c>
     </row>
     <row r="32">
@@ -1561,11 +1561,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>56194</v>
+        <v>76592</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>56194</v>
+        <v>76592</v>
       </c>
     </row>
     <row r="35">
@@ -1629,11 +1629,11 @@
         <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>42796</v>
+        <v>43194</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>42796</v>
+        <v>43194</v>
       </c>
     </row>
     <row r="37">
@@ -1697,11 +1697,11 @@
         <v>40000</v>
       </c>
       <c r="D38" t="n">
-        <v>26998</v>
+        <v>47794</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>119.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>26998</v>
+        <v>47794</v>
       </c>
     </row>
     <row r="39">
@@ -1765,11 +1765,11 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>116794</v>
+        <v>118594</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>107994</v>
+        <v>109794</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>12394</v>
+        <v>13190</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>12394</v>
+        <v>13190</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>200000</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6331.7%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-25200</v>
+        <v>-24802</v>
       </c>
     </row>
     <row r="43">
@@ -1901,11 +1901,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>53056</v>
+        <v>65056</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>53056</v>
+        <v>65056</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>48894</v>
+        <v>49292</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>48894</v>
+        <v>49292</v>
       </c>
     </row>
     <row r="46">
@@ -2003,11 +2003,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>57382</v>
+        <v>69382</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>57382</v>
+        <v>69382</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>49430</v>
+        <v>50824</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>49430</v>
+        <v>50824</v>
       </c>
     </row>
     <row r="49">
@@ -2173,11 +2173,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>28990</v>
+        <v>40990</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>4190</v>
+        <v>16190</v>
       </c>
     </row>
     <row r="53">
@@ -2343,11 +2343,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>2888</v>
+        <v>22688</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>2888</v>
+        <v>22688</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>25190</v>
+        <v>64778</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>25190</v>
+        <v>64778</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>32206</v>
+        <v>71794</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>22006</v>
+        <v>61594</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>13394</v>
+        <v>13792</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>13394</v>
+        <v>13792</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>71099</v>
+        <v>96699</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>71099</v>
+        <v>96699</v>
       </c>
     </row>
     <row r="62">
@@ -2547,11 +2547,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>40322.08</v>
+        <v>48322.08</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>28122.08</v>
+        <v>36122.08</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>23398</v>
+        <v>23796</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8180</v>
+        <v>8578</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>14078</v>
+        <v>14476</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14078</v>
+        <v>14476</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>32000</v>
       </c>
       <c r="D5" t="n">
-        <v>2388</v>
+        <v>2786</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2388</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>90000</v>
       </c>
       <c r="D6" t="n">
-        <v>8000</v>
+        <v>8398</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8000</v>
+        <v>8398</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>37115.34</v>
+        <v>37528.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>36795.34</v>
+        <v>37208.7</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>71100</v>
+        <v>81700</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>68400</v>
+        <v>79000</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>37851.87</v>
+        <v>38987.58</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>370.9%</t>
+          <t>360.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-102548.13</v>
+        <v>-101412.42</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>25900</v>
+        <v>33400</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25900</v>
+        <v>33400</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>107499</v>
+        <v>113141</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>107499</v>
+        <v>113141</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>67423</v>
+        <v>119117</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>67423</v>
+        <v>119117</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>190016</v>
+        <v>250795.96</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>190016</v>
+        <v>250795.96</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>55408.64</v>
+        <v>89992.64000000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>55408.64</v>
+        <v>89992.64000000001</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>48107.5</v>
+        <v>77631</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>48107.5</v>
+        <v>77631</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>195876</v>
+        <v>247058</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>195876</v>
+        <v>247058</v>
       </c>
     </row>
     <row r="18">
@@ -1051,11 +1051,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>38558</v>
+        <v>58956</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>38558</v>
+        <v>58956</v>
       </c>
     </row>
     <row r="20">
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>121986</v>
+        <v>140782</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>117986</v>
+        <v>136782</v>
       </c>
     </row>
     <row r="24">
@@ -1255,11 +1255,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>121462.01</v>
+        <v>128062.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>166.4%</t>
+          <t>175.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>99062.01000000001</v>
+        <v>105662.01</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>81474</v>
+        <v>81774</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>73474</v>
+        <v>73774</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>127337.75</v>
+        <v>143380.25</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>88957.75</v>
+        <v>105000.25</v>
       </c>
     </row>
     <row r="29">
@@ -1425,11 +1425,11 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>65484</v>
+        <v>78584</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>52484</v>
+        <v>65584</v>
       </c>
     </row>
     <row r="31">
@@ -1493,11 +1493,11 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>16992</v>
+        <v>25788</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>8992</v>
+        <v>17788</v>
       </c>
     </row>
     <row r="33">
@@ -1561,11 +1561,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>76592</v>
+        <v>86990</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>76592</v>
+        <v>86990</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>398</v>
+        <v>1194</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>398</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="36">
@@ -1765,11 +1765,11 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>118594</v>
+        <v>118992</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>109794</v>
+        <v>110192</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>13190</v>
+        <v>16190</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>13190</v>
+        <v>16190</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>200000</v>
       </c>
       <c r="D42" t="n">
-        <v>398</v>
+        <v>5398</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>6331.7%</t>
+          <t>466.8%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-24802</v>
+        <v>-19802</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>150000</v>
       </c>
       <c r="D43" t="n">
-        <v>73554</v>
+        <v>77454</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>73554</v>
+        <v>77454</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>65056</v>
+        <v>77454</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>65056</v>
+        <v>77454</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>49292</v>
+        <v>50122</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>49292</v>
+        <v>50122</v>
       </c>
     </row>
     <row r="46">
@@ -2037,11 +2037,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>50824</v>
+        <v>51222</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>50824</v>
+        <v>51222</v>
       </c>
     </row>
     <row r="49">
@@ -2173,11 +2173,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>40990</v>
+        <v>41388</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>16190</v>
+        <v>16588</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>66276</v>
+        <v>82674</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>66276</v>
+        <v>82674</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>24398</v>
+        <v>34398</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>24398</v>
+        <v>34398</v>
       </c>
     </row>
     <row r="55">
@@ -2309,11 +2309,11 @@
         <v>20000</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="57">
@@ -2343,11 +2343,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>22688</v>
+        <v>23086</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>22688</v>
+        <v>23086</v>
       </c>
     </row>
     <row r="58">
@@ -2411,11 +2411,11 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>71794</v>
+        <v>111382</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>61594</v>
+        <v>101182</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>13792</v>
+        <v>14190</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>13792</v>
+        <v>14190</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>96699</v>
+        <v>111173.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>96699</v>
+        <v>111173.8</v>
       </c>
     </row>
     <row r="62">
@@ -2513,23 +2513,23 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>17504.32</v>
+        <v>19707.32</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>412</v>
+        <v>1212</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>17092.32</v>
+        <v>18495.32</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>48322.08</v>
+        <v>82972.98</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>36122.08</v>
+        <v>70772.98</v>
       </c>
     </row>
     <row r="64">
@@ -2615,11 +2615,11 @@
         <v>15378</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>23796</v>
+        <v>23398</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8578</v>
+        <v>8180</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>14476</v>
+        <v>14078</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14476</v>
+        <v>14078</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>32000</v>
       </c>
       <c r="D5" t="n">
-        <v>2786</v>
+        <v>2388</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2786</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="6">
@@ -677,11 +677,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>81700</v>
+        <v>74200</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>79000</v>
+        <v>71500</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>38987.58</v>
+        <v>38589.58</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>360.1%</t>
+          <t>363.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-101412.42</v>
+        <v>-101810.42</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>33400</v>
+        <v>25900</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>33400</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="11">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>77631</v>
+        <v>77581</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>77631</v>
+        <v>77581</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>247058</v>
+        <v>277058</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>247058</v>
+        <v>277058</v>
       </c>
     </row>
     <row r="18">
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>140782</v>
+        <v>140384</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>136782</v>
+        <v>136384</v>
       </c>
     </row>
     <row r="24">
@@ -1255,11 +1255,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>128062.01</v>
+        <v>121462.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>175.4%</t>
+          <t>166.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>105662.01</v>
+        <v>99062.01000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>81774</v>
+        <v>81474</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>73774</v>
+        <v>73474</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>143380.25</v>
+        <v>130738.75</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>105000.25</v>
+        <v>92358.75</v>
       </c>
     </row>
     <row r="29">
@@ -1425,11 +1425,11 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>78584</v>
+        <v>68584</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>65584</v>
+        <v>55584</v>
       </c>
     </row>
     <row r="31">
@@ -1493,11 +1493,11 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>25788</v>
+        <v>17788</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>17788</v>
+        <v>9788</v>
       </c>
     </row>
     <row r="33">
@@ -1561,11 +1561,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>86990</v>
+        <v>76990</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>86990</v>
+        <v>76990</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>1194</v>
+        <v>796</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1194</v>
+        <v>796</v>
       </c>
     </row>
     <row r="36">
@@ -1765,11 +1765,11 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>118992</v>
+        <v>118594</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>110192</v>
+        <v>109794</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>16190</v>
+        <v>14390</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>16190</v>
+        <v>14390</v>
       </c>
     </row>
     <row r="42">
@@ -1901,11 +1901,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>77454</v>
+        <v>77056</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>77454</v>
+        <v>77056</v>
       </c>
     </row>
     <row r="45">
@@ -2037,11 +2037,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>51222</v>
+        <v>50824</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>51222</v>
+        <v>50824</v>
       </c>
     </row>
     <row r="49">
@@ -2173,11 +2173,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>41388</v>
+        <v>40990</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>16588</v>
+        <v>16190</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>82674</v>
+        <v>66276</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>82674</v>
+        <v>66276</v>
       </c>
     </row>
     <row r="54">
@@ -2513,11 +2513,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>19707.32</v>
+        <v>19309.32</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>18495.32</v>
+        <v>18097.32</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>82972.98</v>
+        <v>73219.28</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>70772.98</v>
+        <v>61019.28</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>23398</v>
+        <v>23796</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8180</v>
+        <v>8578</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>14078</v>
+        <v>14476</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14078</v>
+        <v>14476</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>32000</v>
       </c>
       <c r="D5" t="n">
-        <v>2388</v>
+        <v>2786</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2388</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="6">
@@ -677,11 +677,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>74200</v>
+        <v>81700</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>71500</v>
+        <v>79000</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>38589.58</v>
+        <v>38987.58</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>363.8%</t>
+          <t>360.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-101810.42</v>
+        <v>-101412.42</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>25900</v>
+        <v>33400</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25900</v>
+        <v>33400</v>
       </c>
     </row>
     <row r="11">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>77581</v>
+        <v>77631</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>77581</v>
+        <v>77631</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>277058</v>
+        <v>247058</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>277058</v>
+        <v>247058</v>
       </c>
     </row>
     <row r="18">
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>140384</v>
+        <v>140782</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>136384</v>
+        <v>136782</v>
       </c>
     </row>
     <row r="24">
@@ -1255,11 +1255,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>121462.01</v>
+        <v>128062.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>166.4%</t>
+          <t>175.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>99062.01000000001</v>
+        <v>105662.01</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>81474</v>
+        <v>81774</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>73474</v>
+        <v>73774</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>130738.75</v>
+        <v>143380.25</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>92358.75</v>
+        <v>105000.25</v>
       </c>
     </row>
     <row r="29">
@@ -1425,11 +1425,11 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>68584</v>
+        <v>78584</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>55584</v>
+        <v>65584</v>
       </c>
     </row>
     <row r="31">
@@ -1493,11 +1493,11 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>17788</v>
+        <v>25788</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>9788</v>
+        <v>17788</v>
       </c>
     </row>
     <row r="33">
@@ -1561,11 +1561,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>76990</v>
+        <v>86990</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>76990</v>
+        <v>86990</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>796</v>
+        <v>1194</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>796</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="36">
@@ -1765,11 +1765,11 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>118594</v>
+        <v>118992</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>109794</v>
+        <v>110192</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>14390</v>
+        <v>16190</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>14390</v>
+        <v>16190</v>
       </c>
     </row>
     <row r="42">
@@ -1901,11 +1901,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>77056</v>
+        <v>77454</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>77056</v>
+        <v>77454</v>
       </c>
     </row>
     <row r="45">
@@ -2037,11 +2037,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>50824</v>
+        <v>51222</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>50824</v>
+        <v>51222</v>
       </c>
     </row>
     <row r="49">
@@ -2173,11 +2173,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>40990</v>
+        <v>41388</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>16190</v>
+        <v>16588</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>66276</v>
+        <v>82674</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>66276</v>
+        <v>82674</v>
       </c>
     </row>
     <row r="54">
@@ -2513,11 +2513,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>19309.32</v>
+        <v>19707.32</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>18097.32</v>
+        <v>18495.32</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>73219.28</v>
+        <v>82972.98</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>61019.28</v>
+        <v>70772.98</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>77631</v>
+        <v>74387</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>77631</v>
+        <v>74387</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>247058</v>
+        <v>133330</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>247058</v>
+        <v>133330</v>
       </c>
     </row>
     <row r="18">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -507,11 +507,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>93064</v>
+        <v>108064</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>93064</v>
+        <v>108064</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>14476</v>
+        <v>14975</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14476</v>
+        <v>14975</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>32000</v>
       </c>
       <c r="D5" t="n">
-        <v>2786</v>
+        <v>8786</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2786</v>
+        <v>8786</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>90000</v>
       </c>
       <c r="D6" t="n">
-        <v>8398</v>
+        <v>18398</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8398</v>
+        <v>18398</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>37528.7</v>
+        <v>38341.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -655,11 +655,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>37208.7</v>
+        <v>38021.7</v>
       </c>
     </row>
     <row r="8">
@@ -711,11 +711,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>38987.58</v>
+        <v>39287.58</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>360.1%</t>
+          <t>357.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-101412.42</v>
+        <v>-101112.42</v>
       </c>
     </row>
     <row r="10">
@@ -915,11 +915,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>89992.64000000001</v>
+        <v>90400.64000000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>89992.64000000001</v>
+        <v>90400.64000000001</v>
       </c>
     </row>
     <row r="16">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>133330</v>
+        <v>133728</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>133330</v>
+        <v>133728</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>50000</v>
       </c>
       <c r="D18" t="n">
-        <v>10194</v>
+        <v>14174</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>10194</v>
+        <v>14174</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>58956</v>
+        <v>79956</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>58956</v>
+        <v>79956</v>
       </c>
     </row>
     <row r="20">
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>140782</v>
+        <v>141578</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>136782</v>
+        <v>137578</v>
       </c>
     </row>
     <row r="24">
@@ -1255,11 +1255,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>128062.01</v>
+        <v>128460.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>175.4%</t>
+          <t>176.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>105662.01</v>
+        <v>106060.01</v>
       </c>
     </row>
     <row r="26">
@@ -1357,23 +1357,23 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>143380.25</v>
+        <v>153958.15</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>38380</v>
+        <v>40580</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>105000.25</v>
+        <v>113378.15</v>
       </c>
     </row>
     <row r="29">
@@ -1459,11 +1459,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>30196</v>
+        <v>30646.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>30196</v>
+        <v>30646.2</v>
       </c>
     </row>
     <row r="32">
@@ -1629,11 +1629,11 @@
         <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>43194</v>
+        <v>43592</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>43194</v>
+        <v>43592</v>
       </c>
     </row>
     <row r="37">
@@ -1867,11 +1867,11 @@
         <v>150000</v>
       </c>
       <c r="D43" t="n">
-        <v>77454</v>
+        <v>77852</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>77454</v>
+        <v>77852</v>
       </c>
     </row>
     <row r="44">
@@ -2003,11 +2003,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>69382</v>
+        <v>69780</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>69382</v>
+        <v>69780</v>
       </c>
     </row>
     <row r="48">
@@ -2173,11 +2173,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>41388</v>
+        <v>49788</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>16588</v>
+        <v>24988</v>
       </c>
     </row>
     <row r="53">
@@ -2241,11 +2241,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>34398</v>
+        <v>42198</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>34398</v>
+        <v>42198</v>
       </c>
     </row>
     <row r="55">
@@ -2411,11 +2411,11 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>111382</v>
+        <v>116370</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>101182</v>
+        <v>106170</v>
       </c>
     </row>
     <row r="60">
@@ -2479,11 +2479,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>111173.8</v>
+        <v>110854.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>111173.8</v>
+        <v>110854.1</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>19707.32</v>
+        <v>19351.22</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>18495.32</v>
+        <v>18139.22</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>82972.98</v>
+        <v>83370.98</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>70772.98</v>
+        <v>71170.98</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -507,11 +507,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>108064</v>
+        <v>116462</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>116.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>108064</v>
+        <v>116462</v>
       </c>
     </row>
     <row r="4">
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>38341.7</v>
+        <v>38739.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38021.7</v>
+        <v>38419.7</v>
       </c>
     </row>
     <row r="8">
@@ -711,11 +711,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>39287.58</v>
+        <v>49287.58</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>357.4%</t>
+          <t>284.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-101112.42</v>
+        <v>-91112.42</v>
       </c>
     </row>
     <row r="10">
@@ -881,11 +881,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>250795.96</v>
+        <v>259775.96</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>250795.96</v>
+        <v>259775.96</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>90400.64000000001</v>
+        <v>113419.74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>90400.64000000001</v>
+        <v>113419.74</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>74387</v>
+        <v>110706</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>74387</v>
+        <v>110706</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>133728</v>
+        <v>138196</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>133728</v>
+        <v>138196</v>
       </c>
     </row>
     <row r="18">
@@ -1085,11 +1085,11 @@
         <v>50000</v>
       </c>
       <c r="D20" t="n">
-        <v>24800</v>
+        <v>25198</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>24800</v>
+        <v>25198</v>
       </c>
     </row>
     <row r="21">
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>141578</v>
+        <v>153258</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>137578</v>
+        <v>149258</v>
       </c>
     </row>
     <row r="24">
@@ -1255,11 +1255,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>128460.01</v>
+        <v>145060.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>176.0%</t>
+          <t>198.7%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>106060.01</v>
+        <v>122660.01</v>
       </c>
     </row>
     <row r="26">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>153958.15</v>
+        <v>161610.15</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>113378.15</v>
+        <v>121030.15</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>18804.3</v>
+        <v>35604.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>18804.3</v>
+        <v>35604.3</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>78584</v>
+        <v>81684</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>65584</v>
+        <v>68684</v>
       </c>
     </row>
     <row r="31">
@@ -1467,15 +1467,15 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>30646.2</v>
+        <v>26646.2</v>
       </c>
     </row>
     <row r="32">
@@ -1595,11 +1595,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>1194</v>
+        <v>1592</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1194</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="36">
@@ -1799,11 +1799,11 @@
         <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>16190</v>
+        <v>16588</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>16190</v>
+        <v>16588</v>
       </c>
     </row>
     <row r="42">
@@ -1935,11 +1935,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>50122</v>
+        <v>68520</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>50122</v>
+        <v>68520</v>
       </c>
     </row>
     <row r="46">
@@ -2003,11 +2003,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>69780</v>
+        <v>81780</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>69780</v>
+        <v>81780</v>
       </c>
     </row>
     <row r="48">
@@ -2173,11 +2173,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>49788</v>
+        <v>77988</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>24988</v>
+        <v>53188</v>
       </c>
     </row>
     <row r="53">
@@ -2479,11 +2479,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>110854.1</v>
+        <v>111452.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>110854.1</v>
+        <v>111452.1</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>19351.22</v>
+        <v>20347.22</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>18139.22</v>
+        <v>19135.22</v>
       </c>
     </row>
     <row r="63">
@@ -2615,11 +2615,11 @@
         <v>15378</v>
       </c>
       <c r="D65" t="n">
-        <v>398</v>
+        <v>996</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>398</v>
+        <v>996</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -541,11 +541,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>14975</v>
+        <v>15373</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14975</v>
+        <v>15373</v>
       </c>
     </row>
     <row r="5">
@@ -609,11 +609,11 @@
         <v>90000</v>
       </c>
       <c r="D6" t="n">
-        <v>18398</v>
+        <v>18796</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>18398</v>
+        <v>18796</v>
       </c>
     </row>
     <row r="7">
@@ -677,11 +677,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>81700</v>
+        <v>89200</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>79000</v>
+        <v>86500</v>
       </c>
     </row>
     <row r="9">
@@ -881,11 +881,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>259775.96</v>
+        <v>260313.46</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>259775.96</v>
+        <v>260313.46</v>
       </c>
     </row>
     <row r="15">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>110706</v>
+        <v>120706</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>110706</v>
+        <v>120706</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>138196</v>
+        <v>149454</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>138196</v>
+        <v>149454</v>
       </c>
     </row>
     <row r="18">
@@ -1195,15 +1195,15 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4000</v>
+        <v>67588</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>149258</v>
+        <v>85670</v>
       </c>
     </row>
     <row r="24">
@@ -1221,23 +1221,23 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>5398</v>
+        <v>6596</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6600</v>
+        <v>6998</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>106.1%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>-1202</v>
+        <v>-402</v>
       </c>
     </row>
     <row r="25">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>161610.15</v>
+        <v>181610.15</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>121030.15</v>
+        <v>141030.15</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>35604.3</v>
+        <v>50804.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>35604.3</v>
+        <v>50804.3</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>81684</v>
+        <v>89184</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>68684</v>
+        <v>76184</v>
       </c>
     </row>
     <row r="31">
@@ -1467,15 +1467,15 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4000</v>
+        <v>4398</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>26646.2</v>
+        <v>26248.2</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>25788</v>
+        <v>26008</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>17788</v>
+        <v>18008</v>
       </c>
     </row>
     <row r="33">
@@ -1629,11 +1629,11 @@
         <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>43592</v>
+        <v>87392</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>218.5%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>43592</v>
+        <v>87392</v>
       </c>
     </row>
     <row r="37">
@@ -1765,11 +1765,11 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>118992</v>
+        <v>120386</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>110192</v>
+        <v>111586</v>
       </c>
     </row>
     <row r="41">
@@ -1833,11 +1833,11 @@
         <v>200000</v>
       </c>
       <c r="D42" t="n">
-        <v>5398</v>
+        <v>21398</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>466.8%</t>
+          <t>117.8%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-19802</v>
+        <v>-3802</v>
       </c>
     </row>
     <row r="43">
@@ -1969,11 +1969,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>70900</v>
+        <v>71896</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>70900</v>
+        <v>71896</v>
       </c>
     </row>
     <row r="47">
@@ -2139,11 +2139,11 @@
         <v>10000</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="52">
@@ -2173,11 +2173,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>77988</v>
+        <v>85988</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>53188</v>
+        <v>61188</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>82674</v>
+        <v>91674</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>82674</v>
+        <v>91674</v>
       </c>
     </row>
     <row r="54">
@@ -2351,15 +2351,15 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>23086</v>
+        <v>15086</v>
       </c>
     </row>
     <row r="58">
@@ -2385,15 +2385,15 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>64778</v>
+        <v>39978</v>
       </c>
     </row>
     <row r="59">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>14190</v>
+        <v>14588</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>14190</v>
+        <v>14588</v>
       </c>
     </row>
     <row r="61">
@@ -2513,11 +2513,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>20347.22</v>
+        <v>20745.22</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>19135.22</v>
+        <v>19533.22</v>
       </c>
     </row>
     <row r="63">
@@ -2555,15 +2555,15 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>12200</v>
+        <v>15200</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>71170.98</v>
+        <v>68170.98</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>153258</v>
+        <v>173258</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>85670</v>
+        <v>105670</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>6596</v>
+        <v>7796</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>106.1%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>-402</v>
+        <v>798</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>145060.01</v>
+        <v>145360.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>198.7%</t>
+          <t>199.1%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>122660.01</v>
+        <v>122960.01</v>
       </c>
     </row>
     <row r="26">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>23796</v>
+        <v>24194</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8578</v>
+        <v>8976</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>116462</v>
+        <v>120922</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>116.5%</t>
+          <t>120.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>116462</v>
+        <v>120922</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>15373</v>
+        <v>15771</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>15373</v>
+        <v>15771</v>
       </c>
     </row>
     <row r="5">
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>38739.7</v>
+        <v>40054.26</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38419.7</v>
+        <v>39734.26</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>89200</v>
+        <v>104600</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>86500</v>
+        <v>101900</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>49287.58</v>
+        <v>91495.16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>284.9%</t>
+          <t>153.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-91112.42</v>
+        <v>-48904.84</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>33400</v>
+        <v>34200</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>33400</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>113141</v>
+        <v>140594</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>113141</v>
+        <v>140594</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>119117</v>
+        <v>127107</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>119117</v>
+        <v>127107</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>260313.46</v>
+        <v>342616.53</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>260313.46</v>
+        <v>342616.53</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>113419.74</v>
+        <v>132533.74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>113419.74</v>
+        <v>132533.74</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>120706</v>
+        <v>155847</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>120706</v>
+        <v>155847</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>149454</v>
+        <v>187218</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>149454</v>
+        <v>187218</v>
       </c>
     </row>
     <row r="18">
@@ -1051,11 +1051,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>79956</v>
+        <v>109956</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>79956</v>
+        <v>109956</v>
       </c>
     </row>
     <row r="20">
@@ -1119,11 +1119,11 @@
         <v>100000</v>
       </c>
       <c r="D21" t="n">
-        <v>58396.00000000001</v>
+        <v>58794.00000000001</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>58396.00000000001</v>
+        <v>58794.00000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1161,15 +1161,15 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>12444.48</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>28080</v>
+        <v>15635.52</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>173258</v>
+        <v>198748</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>105670</v>
+        <v>131160</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>7796</v>
+        <v>53192.01</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>798</v>
+        <v>46194.01</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>145360.01</v>
+        <v>148357.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>199.1%</t>
+          <t>203.2%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>122960.01</v>
+        <v>125957.01</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>50000</v>
       </c>
       <c r="D26" t="n">
-        <v>398</v>
+        <v>5358</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>398</v>
+        <v>5358</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>81774</v>
+        <v>106168</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>106.2%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>73774</v>
+        <v>98168</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>181610.15</v>
+        <v>218157.55</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>141030.15</v>
+        <v>177577.55</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>50804.3</v>
+        <v>70808.89999999999</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>50804.3</v>
+        <v>70808.89999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>89184</v>
+        <v>97484</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>76184</v>
+        <v>84484</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>30646.2</v>
+        <v>41746.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>26248.2</v>
+        <v>37348.2</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>26008</v>
+        <v>26406</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>18008</v>
+        <v>18406</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>50000</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>86990</v>
+        <v>107388</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>86990</v>
+        <v>107388</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>1592</v>
+        <v>8192</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1592</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>87392</v>
+        <v>87790</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>218.5%</t>
+          <t>219.5%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>87392</v>
+        <v>87790</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>80000</v>
       </c>
       <c r="D37" t="n">
-        <v>21592</v>
+        <v>41990</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>19912</v>
+        <v>40310</v>
       </c>
     </row>
     <row r="38">
@@ -1697,11 +1697,11 @@
         <v>40000</v>
       </c>
       <c r="D38" t="n">
-        <v>47794</v>
+        <v>37794</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>119.5%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>47794</v>
+        <v>37794</v>
       </c>
     </row>
     <row r="39">
@@ -1765,11 +1765,11 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>120386</v>
+        <v>137186</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>111586</v>
+        <v>128386</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>16588</v>
+        <v>66588</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>16588</v>
+        <v>66588</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>200000</v>
       </c>
       <c r="D42" t="n">
-        <v>21398</v>
+        <v>21796</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>117.8%</t>
+          <t>115.6%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-3802</v>
+        <v>-3404</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>150000</v>
       </c>
       <c r="D43" t="n">
-        <v>77852</v>
+        <v>79250</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>77852</v>
+        <v>79250</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>77454</v>
+        <v>98052</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>77454</v>
+        <v>98052</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>68520</v>
+        <v>97219.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>68520</v>
+        <v>97219.2</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>71896</v>
+        <v>126896</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>71896</v>
+        <v>126896</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>81780</v>
+        <v>83178</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>81780</v>
+        <v>83178</v>
       </c>
     </row>
     <row r="48">
@@ -2173,11 +2173,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>85988</v>
+        <v>86784</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>61188</v>
+        <v>61984</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>91674</v>
+        <v>99674</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>91674</v>
+        <v>99674</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>42198</v>
+        <v>58596</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>42198</v>
+        <v>58596</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>48000</v>
       </c>
       <c r="D55" t="n">
-        <v>2796</v>
+        <v>3796</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>2796</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="56">
@@ -2343,11 +2343,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>23086</v>
+        <v>35086</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>15086</v>
+        <v>27086</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>64778</v>
+        <v>77176</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>39978</v>
+        <v>52376</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>116370</v>
+        <v>122768</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>102.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>106170</v>
+        <v>112568</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>14588</v>
+        <v>15388</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>14588</v>
+        <v>15388</v>
       </c>
     </row>
     <row r="61">
@@ -2479,23 +2479,23 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>111452.1</v>
+        <v>172052.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>111452.1</v>
+        <v>162052.6</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>20745.22</v>
+        <v>55410.62</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>19533.22</v>
+        <v>54198.62</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>83370.98</v>
+        <v>105093.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>68170.98</v>
+        <v>89893.48</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>40054.26</v>
+        <v>41338.32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>39734.26</v>
+        <v>41018.32</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>104600</v>
+        <v>105400</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>101900</v>
+        <v>102700</v>
       </c>
     </row>
     <row r="9">
@@ -813,11 +813,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>140594</v>
+        <v>153540</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>140594</v>
+        <v>153540</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>127107</v>
+        <v>131234</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>127107</v>
+        <v>131234</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>342616.53</v>
+        <v>349943.53</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>342616.53</v>
+        <v>349943.53</v>
       </c>
     </row>
     <row r="15">
@@ -1051,11 +1051,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>109956</v>
+        <v>94956</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>109956</v>
+        <v>94956</v>
       </c>
     </row>
     <row r="20">
@@ -1153,11 +1153,11 @@
         <v>100000</v>
       </c>
       <c r="D22" t="n">
-        <v>28080</v>
+        <v>44478</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>15635.52</v>
+        <v>32033.52</v>
       </c>
     </row>
     <row r="23">
@@ -1221,11 +1221,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>53192.01</v>
+        <v>53590.01</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>46194.01</v>
+        <v>46592.01</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>148357.01</v>
+        <v>153755.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>203.2%</t>
+          <t>210.6%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>125957.01</v>
+        <v>131355.01</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>106168</v>
+        <v>113166</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>106.2%</t>
+          <t>113.2%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>98168</v>
+        <v>105166</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>218157.55</v>
+        <v>247261.65</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>177577.55</v>
+        <v>206681.65</v>
       </c>
     </row>
     <row r="29">
@@ -1459,23 +1459,23 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>41746.2</v>
+        <v>44846.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4398</v>
+        <v>4498</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>37348.2</v>
+        <v>40348.2</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>26406</v>
+        <v>31406</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>18406</v>
+        <v>23406</v>
       </c>
     </row>
     <row r="33">
@@ -1561,23 +1561,23 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>107388</v>
+        <v>137786</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>107388</v>
+        <v>137556</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>8192</v>
+        <v>8590</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8192</v>
+        <v>8590</v>
       </c>
     </row>
     <row r="36">
@@ -1697,11 +1697,11 @@
         <v>40000</v>
       </c>
       <c r="D38" t="n">
-        <v>37794</v>
+        <v>47794</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>119.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>37794</v>
+        <v>47794</v>
       </c>
     </row>
     <row r="39">
@@ -1807,15 +1807,15 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>66588</v>
+        <v>56588</v>
       </c>
     </row>
     <row r="42">
@@ -1867,11 +1867,11 @@
         <v>150000</v>
       </c>
       <c r="D43" t="n">
-        <v>79250</v>
+        <v>99050</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>79250</v>
+        <v>99050</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>98052</v>
+        <v>168452</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>112.3%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>98052</v>
+        <v>168452</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>97219.2</v>
+        <v>98019.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>97219.2</v>
+        <v>98019.2</v>
       </c>
     </row>
     <row r="46">
@@ -2173,11 +2173,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>86784</v>
+        <v>95284</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>61984</v>
+        <v>70484</v>
       </c>
     </row>
     <row r="53">
@@ -2215,15 +2215,15 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>16800</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>99674</v>
+        <v>82874</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>58596</v>
+        <v>59596</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>58596</v>
+        <v>59596</v>
       </c>
     </row>
     <row r="55">
@@ -2343,11 +2343,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>35086</v>
+        <v>59886</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>27086</v>
+        <v>51886</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>77176</v>
+        <v>85574</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>52376</v>
+        <v>60774</v>
       </c>
     </row>
     <row r="59">
@@ -2479,11 +2479,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>172052.6</v>
+        <v>180052.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2491,11 +2491,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>162052.6</v>
+        <v>170052.6</v>
       </c>
     </row>
     <row r="62">
@@ -2513,23 +2513,23 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>55410.62</v>
+        <v>63410.62</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1212</v>
+        <v>15212</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>54198.62</v>
+        <v>48198.62</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>105093.48</v>
+        <v>105691.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>89893.48</v>
+        <v>90491.48</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>24194</v>
+        <v>28154</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8976</v>
+        <v>12936</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>120922</v>
+        <v>126922</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>120.9%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>120922</v>
+        <v>126922</v>
       </c>
     </row>
     <row r="4">
@@ -711,11 +711,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>91495.16</v>
+        <v>101930.92</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>153.5%</t>
+          <t>137.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-48904.84</v>
+        <v>-38469.08</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>34200</v>
+        <v>35000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>34200</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="11">
@@ -1051,11 +1051,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>94956</v>
+        <v>116936</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94956</v>
+        <v>116936</v>
       </c>
     </row>
     <row r="20">
@@ -1119,11 +1119,11 @@
         <v>100000</v>
       </c>
       <c r="D21" t="n">
-        <v>58794.00000000001</v>
+        <v>60774.00000000001</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>58794.00000000001</v>
+        <v>60774.00000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>198748</v>
+        <v>218748</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>131160</v>
+        <v>151160</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>53590.01</v>
+        <v>63590.01</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>46592.01</v>
+        <v>56592.01</v>
       </c>
     </row>
     <row r="25">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>247261.65</v>
+        <v>247659.65</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>206681.65</v>
+        <v>207079.65</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>70808.89999999999</v>
+        <v>71406.89999999999</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>70808.89999999999</v>
+        <v>71406.89999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1765,11 +1765,11 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>137186</v>
+        <v>143186</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>128386</v>
+        <v>134386</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>66588</v>
+        <v>66986</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1811,11 +1811,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>56588</v>
+        <v>56986</v>
       </c>
     </row>
     <row r="42">
@@ -1867,11 +1867,11 @@
         <v>150000</v>
       </c>
       <c r="D43" t="n">
-        <v>99050</v>
+        <v>105650</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>99050</v>
+        <v>105650</v>
       </c>
     </row>
     <row r="44">
@@ -1901,11 +1901,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>168452</v>
+        <v>184248</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>112.3%</t>
+          <t>122.8%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>168452</v>
+        <v>184248</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>98019.2</v>
+        <v>98617.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>98019.2</v>
+        <v>98617.2</v>
       </c>
     </row>
     <row r="46">
@@ -2003,11 +2003,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>83178</v>
+        <v>83576</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>83178</v>
+        <v>83576</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>51222</v>
+        <v>51620</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>51222</v>
+        <v>51620</v>
       </c>
     </row>
     <row r="49">
@@ -2173,23 +2173,23 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>95284</v>
+        <v>103284</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>24800</v>
+        <v>28800</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>70484</v>
+        <v>74484</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>99674</v>
+        <v>114068</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>82874</v>
+        <v>97268</v>
       </c>
     </row>
     <row r="54">
@@ -2377,23 +2377,23 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>85574</v>
+        <v>91574</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>24800</v>
+        <v>34800</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>60774</v>
+        <v>56774</v>
       </c>
     </row>
     <row r="59">
@@ -2445,11 +2445,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>15388</v>
+        <v>28584</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>15388</v>
+        <v>28584</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>180052.6</v>
+        <v>181732.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2491,11 +2491,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>170052.6</v>
+        <v>171732.6</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>63410.62</v>
+        <v>63642.52</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>48198.62</v>
+        <v>48430.52</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>105691.48</v>
+        <v>106089.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>90491.48</v>
+        <v>90889.48</v>
       </c>
     </row>
     <row r="64">
@@ -2615,11 +2615,11 @@
         <v>15378</v>
       </c>
       <c r="D65" t="n">
-        <v>996</v>
+        <v>17394</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>996</v>
+        <v>17394</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>28154</v>
+        <v>40552</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>12936</v>
+        <v>25334</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>15771</v>
+        <v>16969</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>15771</v>
+        <v>16969</v>
       </c>
     </row>
     <row r="5">
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>41338.32</v>
+        <v>46736.32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -655,11 +655,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>41018.32</v>
+        <v>46416.32</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>105400</v>
+        <v>111600</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>102700</v>
+        <v>108900</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>101930.92</v>
+        <v>119930.92</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>99.9%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>137.7%</t>
+          <t>117.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-38469.08</v>
+        <v>-20469.08</v>
       </c>
     </row>
     <row r="10">
@@ -813,11 +813,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>153540</v>
+        <v>160607.57</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>153540</v>
+        <v>160607.57</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>131234</v>
+        <v>133034</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>131234</v>
+        <v>133034</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>349943.53</v>
+        <v>362051.74</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>349943.53</v>
+        <v>362051.74</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>132533.74</v>
+        <v>147722.74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>132533.74</v>
+        <v>147722.74</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>155847</v>
+        <v>148212</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>155847</v>
+        <v>148212</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>187218</v>
+        <v>211319</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>187218</v>
+        <v>211319</v>
       </c>
     </row>
     <row r="18">
@@ -1051,11 +1051,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>116936</v>
+        <v>125473</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>116936</v>
+        <v>125473</v>
       </c>
     </row>
     <row r="20">
@@ -1153,11 +1153,11 @@
         <v>100000</v>
       </c>
       <c r="D22" t="n">
-        <v>44478</v>
+        <v>46278</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>32033.52</v>
+        <v>33833.52</v>
       </c>
     </row>
     <row r="23">
@@ -1187,23 +1187,23 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>218748</v>
+        <v>231948</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>67588</v>
+        <v>92388</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>151160</v>
+        <v>139560</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>63590.01</v>
+        <v>64988.01</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>56592.01</v>
+        <v>57990.01</v>
       </c>
     </row>
     <row r="25">
@@ -1289,11 +1289,11 @@
         <v>50000</v>
       </c>
       <c r="D26" t="n">
-        <v>5358</v>
+        <v>11958</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5358</v>
+        <v>11958</v>
       </c>
     </row>
     <row r="27">
@@ -1323,11 +1323,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>113166</v>
+        <v>115146</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>113.2%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>105166</v>
+        <v>107146</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>247659.65</v>
+        <v>248408.35</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>207079.65</v>
+        <v>207828.35</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>71406.89999999999</v>
+        <v>83406.89999999999</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>71406.89999999999</v>
+        <v>83406.89999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1629,11 +1629,11 @@
         <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>87790</v>
+        <v>88188</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>219.5%</t>
+          <t>220.5%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>87790</v>
+        <v>88188</v>
       </c>
     </row>
     <row r="37">
@@ -1901,11 +1901,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>184248</v>
+        <v>185044</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>122.8%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>184248</v>
+        <v>185044</v>
       </c>
     </row>
     <row r="45">
@@ -1969,11 +1969,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>126896</v>
+        <v>134896</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>126896</v>
+        <v>134896</v>
       </c>
     </row>
     <row r="47">
@@ -2011,15 +2011,15 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>16800</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>83576</v>
+        <v>66776</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>51620</v>
+        <v>52218</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>51620</v>
+        <v>52218</v>
       </c>
     </row>
     <row r="49">
@@ -2207,11 +2207,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>114068</v>
+        <v>127068</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>97268</v>
+        <v>110268</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>59596</v>
+        <v>59994</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>59596</v>
+        <v>59994</v>
       </c>
     </row>
     <row r="55">
@@ -2411,11 +2411,11 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>122768</v>
+        <v>131166</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>102.3%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>112568</v>
+        <v>120966</v>
       </c>
     </row>
     <row r="60">
@@ -2513,11 +2513,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>63642.52</v>
+        <v>64040.52</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>48430.52</v>
+        <v>48828.52</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>106089.48</v>
+        <v>106885.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>90889.48</v>
+        <v>91685.48</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -541,11 +541,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>16969</v>
+        <v>17367</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>16969</v>
+        <v>17367</v>
       </c>
     </row>
     <row r="5">
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>46736.32</v>
+        <v>54736.32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -655,11 +655,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>46416.32</v>
+        <v>54416.32</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>111600</v>
+        <v>126600</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>105.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>108900</v>
+        <v>123900</v>
       </c>
     </row>
     <row r="9">
@@ -745,11 +745,11 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>35000</v>
+        <v>42500</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>35000</v>
+        <v>42500</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>160607.57</v>
+        <v>153188.57</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>160607.57</v>
+        <v>153188.57</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>133034</v>
+        <v>131734</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>133034</v>
+        <v>131734</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>362051.74</v>
+        <v>369470.74</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>362051.74</v>
+        <v>369470.74</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>147722.74</v>
+        <v>149022.74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>147722.74</v>
+        <v>149022.74</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>148212</v>
+        <v>162373</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>148212</v>
+        <v>162373</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>211319</v>
+        <v>237319</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>211319</v>
+        <v>237319</v>
       </c>
     </row>
     <row r="18">
@@ -1051,11 +1051,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>125473</v>
+        <v>126871</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>125473</v>
+        <v>126871</v>
       </c>
     </row>
     <row r="20">
@@ -1153,11 +1153,11 @@
         <v>100000</v>
       </c>
       <c r="D22" t="n">
-        <v>46278</v>
+        <v>46676</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>33833.52</v>
+        <v>34231.52</v>
       </c>
     </row>
     <row r="23">
@@ -1221,11 +1221,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>64988.01</v>
+        <v>65386.01</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>57990.01</v>
+        <v>58388.01</v>
       </c>
     </row>
     <row r="25">
@@ -1323,11 +1323,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>115146</v>
+        <v>123146</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>107146</v>
+        <v>115146</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>248408.35</v>
+        <v>258477.95</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>207828.35</v>
+        <v>217897.95</v>
       </c>
     </row>
     <row r="29">
@@ -1425,11 +1425,11 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>97484</v>
+        <v>98284</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>84484</v>
+        <v>85284</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>44846.2</v>
+        <v>45846.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>40348.2</v>
+        <v>41348.2</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>31406</v>
+        <v>31804</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>23406</v>
+        <v>23804</v>
       </c>
     </row>
     <row r="33">
@@ -1561,11 +1561,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>137786</v>
+        <v>147786</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>137556</v>
+        <v>147556</v>
       </c>
     </row>
     <row r="35">
@@ -1629,11 +1629,11 @@
         <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>88188</v>
+        <v>109868</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>220.5%</t>
+          <t>274.7%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>88188</v>
+        <v>109868</v>
       </c>
     </row>
     <row r="37">
@@ -1901,11 +1901,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>185044</v>
+        <v>222844</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>148.6%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>185044</v>
+        <v>222844</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>98617.2</v>
+        <v>108617.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>98617.2</v>
+        <v>108617.2</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>134896</v>
+        <v>147294</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>134896</v>
+        <v>147294</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>83576</v>
+        <v>84576</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>66776</v>
+        <v>67776</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>52218</v>
+        <v>64218</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>52218</v>
+        <v>64218</v>
       </c>
     </row>
     <row r="49">
@@ -2309,11 +2309,11 @@
         <v>20000</v>
       </c>
       <c r="D56" t="n">
-        <v>6600</v>
+        <v>7998</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>6600</v>
+        <v>7998</v>
       </c>
     </row>
     <row r="57">
@@ -2343,11 +2343,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>59886</v>
+        <v>69886</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>51886</v>
+        <v>61886</v>
       </c>
     </row>
     <row r="58">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>40552</v>
+        <v>41449</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>25334</v>
+        <v>26231</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>17367</v>
+        <v>16868</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>17367</v>
+        <v>16868</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>32000</v>
       </c>
       <c r="D5" t="n">
-        <v>8786</v>
+        <v>9184</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8786</v>
+        <v>9184</v>
       </c>
     </row>
     <row r="6">
@@ -677,11 +677,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>126600</v>
+        <v>133200</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>105.5%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -689,11 +689,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>123900</v>
+        <v>130500</v>
       </c>
     </row>
     <row r="9">
@@ -813,11 +813,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>153188.57</v>
+        <v>167718.57</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>153188.57</v>
+        <v>167718.57</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>131734</v>
+        <v>110514.5700000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>131734</v>
+        <v>110514.5700000001</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>369470.74</v>
+        <v>389091.74</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>369470.74</v>
+        <v>389091.74</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>149022.74</v>
+        <v>174372.74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>149022.74</v>
+        <v>174372.74</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>162373</v>
+        <v>185773</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>162373</v>
+        <v>185773</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>237319</v>
+        <v>237717</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>237319</v>
+        <v>237717</v>
       </c>
     </row>
     <row r="18">
@@ -1153,11 +1153,11 @@
         <v>100000</v>
       </c>
       <c r="D22" t="n">
-        <v>46676</v>
+        <v>47074</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>34231.52</v>
+        <v>34629.52</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>231948</v>
+        <v>251168</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>139560</v>
+        <v>158780</v>
       </c>
     </row>
     <row r="24">
@@ -1323,11 +1323,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>123146</v>
+        <v>123544</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>115146</v>
+        <v>115544</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>258477.95</v>
+        <v>259075.95</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>217897.95</v>
+        <v>218495.95</v>
       </c>
     </row>
     <row r="29">
@@ -1425,11 +1425,11 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>98284</v>
+        <v>99084</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>85284</v>
+        <v>86084</v>
       </c>
     </row>
     <row r="31">
@@ -1527,11 +1527,11 @@
         <v>50000</v>
       </c>
       <c r="D33" t="n">
-        <v>398</v>
+        <v>8398</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>398</v>
+        <v>8398</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>147786</v>
+        <v>148184</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>147556</v>
+        <v>147954</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>8590</v>
+        <v>18590</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8590</v>
+        <v>18590</v>
       </c>
     </row>
     <row r="36">
@@ -1765,11 +1765,11 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>143186</v>
+        <v>140186</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1777,11 +1777,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>134386</v>
+        <v>131386</v>
       </c>
     </row>
     <row r="41">
@@ -1935,11 +1935,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>108617.2</v>
+        <v>119613.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>108617.2</v>
+        <v>119613.2</v>
       </c>
     </row>
     <row r="46">
@@ -2003,11 +2003,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>84576</v>
+        <v>84974</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>67776</v>
+        <v>68174</v>
       </c>
     </row>
     <row r="48">
@@ -2173,11 +2173,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>103284</v>
+        <v>95284</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>74484</v>
+        <v>66484</v>
       </c>
     </row>
     <row r="53">
@@ -2241,11 +2241,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>59994</v>
+        <v>69592</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>59994</v>
+        <v>69592</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>48000</v>
       </c>
       <c r="D55" t="n">
-        <v>3796</v>
+        <v>13796</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>3796</v>
+        <v>13796</v>
       </c>
     </row>
     <row r="56">
@@ -2377,11 +2377,11 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>91574</v>
+        <v>89574</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>56774</v>
+        <v>54774</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>131166</v>
+        <v>134166</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>111.8%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>120966</v>
+        <v>123966</v>
       </c>
     </row>
     <row r="60">
@@ -2479,23 +2479,23 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>181732.6</v>
+        <v>214532.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>171732.6</v>
+        <v>194532.6</v>
       </c>
     </row>
     <row r="62">
@@ -2547,23 +2547,23 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>106885.48</v>
+        <v>128279.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>15200</v>
+        <v>37000</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>91685.48</v>
+        <v>91279.48</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>54736.32</v>
+        <v>54936.32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>54416.32</v>
+        <v>54616.32</v>
       </c>
     </row>
     <row r="8">
@@ -711,11 +711,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>119930.92</v>
+        <v>120560.17</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>99.9%</t>
+          <t>100.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>117.1%</t>
+          <t>116.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-20469.08</v>
+        <v>-19839.83</v>
       </c>
     </row>
     <row r="10">
@@ -2479,11 +2479,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>214532.6</v>
+        <v>215067.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>194532.6</v>
+        <v>195067.5</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>64040.52</v>
+        <v>66135.72</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>48828.52</v>
+        <v>50923.72</v>
       </c>
     </row>
     <row r="63">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -507,11 +507,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>126922</v>
+        <v>127320</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>126922</v>
+        <v>127320</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>16868</v>
+        <v>28868</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>120.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>16868</v>
+        <v>28868</v>
       </c>
     </row>
     <row r="5">
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>54936.32</v>
+        <v>56884.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>54616.32</v>
+        <v>56564.6</v>
       </c>
     </row>
     <row r="8">
@@ -813,11 +813,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>167718.57</v>
+        <v>220339.57</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>167718.57</v>
+        <v>220339.57</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>110514.5700000001</v>
+        <v>121610.5700000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>110514.5700000001</v>
+        <v>121610.5700000001</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>389091.74</v>
+        <v>394578.74</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>389091.74</v>
+        <v>394578.74</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>174372.74</v>
+        <v>204409.74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>174372.74</v>
+        <v>204409.74</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>185773</v>
+        <v>174905</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>185773</v>
+        <v>174905</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>237717</v>
+        <v>248911</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>237717</v>
+        <v>248911</v>
       </c>
     </row>
     <row r="18">
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>251168</v>
+        <v>311964</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>111.4%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>158780</v>
+        <v>219576</v>
       </c>
     </row>
     <row r="24">
@@ -1255,11 +1255,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>153755.01</v>
+        <v>154153.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>210.6%</t>
+          <t>211.2%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>131355.01</v>
+        <v>131753.01</v>
       </c>
     </row>
     <row r="26">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>259075.95</v>
+        <v>270093.55</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>218495.95</v>
+        <v>229513.55</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>83406.89999999999</v>
+        <v>100906.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>83406.89999999999</v>
+        <v>100906.9</v>
       </c>
     </row>
     <row r="30">
@@ -1459,11 +1459,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>45846.2</v>
+        <v>82364.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>41348.2</v>
+        <v>77866.2</v>
       </c>
     </row>
     <row r="32">
@@ -1493,11 +1493,11 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>31804</v>
+        <v>51804</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1505,11 +1505,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>23804</v>
+        <v>43804</v>
       </c>
     </row>
     <row r="33">
@@ -1595,11 +1595,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>18590</v>
+        <v>28590</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>18590</v>
+        <v>28590</v>
       </c>
     </row>
     <row r="36">
@@ -1629,11 +1629,11 @@
         <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>109868</v>
+        <v>110266</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>274.7%</t>
+          <t>275.7%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>109868</v>
+        <v>110266</v>
       </c>
     </row>
     <row r="37">
@@ -1663,11 +1663,11 @@
         <v>80000</v>
       </c>
       <c r="D37" t="n">
-        <v>41990</v>
+        <v>42388</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>40310</v>
+        <v>40708</v>
       </c>
     </row>
     <row r="38">
@@ -1697,11 +1697,11 @@
         <v>40000</v>
       </c>
       <c r="D38" t="n">
-        <v>47794</v>
+        <v>48192</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>119.5%</t>
+          <t>120.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>47794</v>
+        <v>48192</v>
       </c>
     </row>
     <row r="39">
@@ -1935,11 +1935,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>119613.2</v>
+        <v>136613.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>119613.2</v>
+        <v>136613.2</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>147294</v>
+        <v>165294</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>147294</v>
+        <v>165294</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>84974</v>
+        <v>92974</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>68174</v>
+        <v>76174</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>64218</v>
+        <v>72218</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>64218</v>
+        <v>72218</v>
       </c>
     </row>
     <row r="49">
@@ -2173,11 +2173,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>95284</v>
+        <v>113682</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>66484</v>
+        <v>84882</v>
       </c>
     </row>
     <row r="53">
@@ -2343,11 +2343,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>69886</v>
+        <v>70284</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>61886</v>
+        <v>62284</v>
       </c>
     </row>
     <row r="58">
@@ -2411,11 +2411,11 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>134166</v>
+        <v>134962</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>111.8%</t>
+          <t>112.5%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>123966</v>
+        <v>124762</v>
       </c>
     </row>
     <row r="60">
@@ -2479,11 +2479,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>215067.5</v>
+        <v>288078.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2491,11 +2491,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>195067.5</v>
+        <v>268078.1</v>
       </c>
     </row>
     <row r="62">
@@ -2513,7 +2513,7 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>66135.72</v>
+        <v>66169.62</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>50923.72</v>
+        <v>50957.62</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>128279.48</v>
+        <v>136279.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>91279.48</v>
+        <v>99279.48000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2581,11 +2581,11 @@
         <v>20796</v>
       </c>
       <c r="D64" t="n">
-        <v>398</v>
+        <v>796</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>398</v>
+        <v>796</v>
       </c>
     </row>
     <row r="65">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -507,11 +507,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>127320</v>
+        <v>131280</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>131.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>127320</v>
+        <v>131280</v>
       </c>
     </row>
     <row r="4">
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>56884.6</v>
+        <v>64884.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -655,11 +655,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>56564.6</v>
+        <v>64564.6</v>
       </c>
     </row>
     <row r="8">
@@ -711,11 +711,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>120560.17</v>
+        <v>138885.26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>100.5%</t>
+          <t>115.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>116.5%</t>
+          <t>101.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-19839.83</v>
+        <v>-1514.739999999991</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>42500</v>
+        <v>43300</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>42500</v>
+        <v>43300</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>220339.57</v>
+        <v>259421.14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>220339.57</v>
+        <v>259421.14</v>
       </c>
     </row>
     <row r="13">
@@ -847,11 +847,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>121610.5700000001</v>
+        <v>145375.5700000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>121610.5700000001</v>
+        <v>145375.5700000001</v>
       </c>
     </row>
     <row r="14">
@@ -881,11 +881,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>394578.74</v>
+        <v>437595.74</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>394578.74</v>
+        <v>437595.74</v>
       </c>
     </row>
     <row r="15">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>174905</v>
+        <v>184905</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>174905</v>
+        <v>184905</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>248911</v>
+        <v>270507</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>248911</v>
+        <v>270507</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>50000</v>
       </c>
       <c r="D18" t="n">
-        <v>14174</v>
+        <v>19174</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>14174</v>
+        <v>19174</v>
       </c>
     </row>
     <row r="19">
@@ -1119,11 +1119,11 @@
         <v>100000</v>
       </c>
       <c r="D21" t="n">
-        <v>60774.00000000001</v>
+        <v>80774</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>60774.00000000001</v>
+        <v>80774</v>
       </c>
     </row>
     <row r="22">
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>311964</v>
+        <v>318564</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>113.8%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>219576</v>
+        <v>226176</v>
       </c>
     </row>
     <row r="24">
@@ -1255,11 +1255,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>154153.01</v>
+        <v>166153.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>211.2%</t>
+          <t>227.6%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>131753.01</v>
+        <v>143753.01</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>123544</v>
+        <v>133544</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>133.5%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>115544</v>
+        <v>125544</v>
       </c>
     </row>
     <row r="28">
@@ -1357,11 +1357,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>270093.55</v>
+        <v>274354.45</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>101.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1369,11 +1369,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>229513.55</v>
+        <v>233774.45</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>100906.9</v>
+        <v>118406.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>100906.9</v>
+        <v>118406.9</v>
       </c>
     </row>
     <row r="30">
@@ -1459,11 +1459,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>82364.2</v>
+        <v>90364.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>77866.2</v>
+        <v>85866.2</v>
       </c>
     </row>
     <row r="32">
@@ -1595,11 +1595,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>28590</v>
+        <v>28988</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>28590</v>
+        <v>28988</v>
       </c>
     </row>
     <row r="36">
@@ -1663,11 +1663,11 @@
         <v>80000</v>
       </c>
       <c r="D37" t="n">
-        <v>42388</v>
+        <v>42786</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>40708</v>
+        <v>41106</v>
       </c>
     </row>
     <row r="38">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="40">
@@ -1799,11 +1799,11 @@
         <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>66986</v>
+        <v>77782</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1811,11 +1811,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>56986</v>
+        <v>67782</v>
       </c>
     </row>
     <row r="42">
@@ -1901,11 +1901,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>222844</v>
+        <v>230844</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>148.6%</t>
+          <t>153.9%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>222844</v>
+        <v>230844</v>
       </c>
     </row>
     <row r="45">
@@ -1935,11 +1935,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>136613.2</v>
+        <v>194663.28</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>136613.2</v>
+        <v>194663.28</v>
       </c>
     </row>
     <row r="46">
@@ -1969,11 +1969,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>165294</v>
+        <v>173294</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>165294</v>
+        <v>173294</v>
       </c>
     </row>
     <row r="47">
@@ -2003,11 +2003,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>92974</v>
+        <v>101372</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2015,11 +2015,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>76174</v>
+        <v>84572</v>
       </c>
     </row>
     <row r="48">
@@ -2207,11 +2207,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>127068</v>
+        <v>134464</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>110268</v>
+        <v>117664</v>
       </c>
     </row>
     <row r="54">
@@ -2377,11 +2377,11 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>89574</v>
+        <v>89972</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>54774</v>
+        <v>55172</v>
       </c>
     </row>
     <row r="59">
@@ -2479,11 +2479,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>288078.1</v>
+        <v>316931.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2491,11 +2491,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>268078.1</v>
+        <v>296931.5</v>
       </c>
     </row>
     <row r="62">
@@ -2547,11 +2547,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>136279.48</v>
+        <v>181673.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>99279.48000000001</v>
+        <v>144673.48</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>41449</v>
+        <v>53449</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>26231</v>
+        <v>38231</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>131280</v>
+        <v>143880</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>131.3%</t>
+          <t>143.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>131280</v>
+        <v>143880</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>28868</v>
+        <v>46868</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>120.3%</t>
+          <t>195.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>28868</v>
+        <v>46868</v>
       </c>
     </row>
     <row r="5">
@@ -643,11 +643,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>64884.6</v>
+        <v>73224.69</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -655,11 +655,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>64564.6</v>
+        <v>72904.69</v>
       </c>
     </row>
     <row r="8">
@@ -685,15 +685,15 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2700</v>
+        <v>18150</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>130500</v>
+        <v>115050</v>
       </c>
     </row>
     <row r="9">
@@ -719,15 +719,15 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>140400</v>
+        <v>142900</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>101.1%</t>
+          <t>102.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-1514.739999999991</v>
+        <v>-4014.739999999991</v>
       </c>
     </row>
     <row r="10">
@@ -745,23 +745,23 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>43300</v>
+        <v>44100</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>43300</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="11">
@@ -813,11 +813,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>259421.14</v>
+        <v>307177.14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>102.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>259421.14</v>
+        <v>307177.14</v>
       </c>
     </row>
     <row r="13">
@@ -881,11 +881,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>437595.74</v>
+        <v>468749.74</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>117.2%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>437595.74</v>
+        <v>468749.74</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>204409.74</v>
+        <v>206846.74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>204409.74</v>
+        <v>206846.74</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>184905</v>
+        <v>190303</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>184905</v>
+        <v>190303</v>
       </c>
     </row>
     <row r="17">
@@ -1051,11 +1051,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>126871</v>
+        <v>127871</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>126871</v>
+        <v>127871</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>50000</v>
       </c>
       <c r="D20" t="n">
-        <v>25198</v>
+        <v>33596</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>25198</v>
+        <v>33596</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>100000</v>
       </c>
       <c r="D21" t="n">
-        <v>80774</v>
+        <v>91172</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>80774</v>
+        <v>91172</v>
       </c>
     </row>
     <row r="22">
@@ -1153,11 +1153,11 @@
         <v>100000</v>
       </c>
       <c r="D22" t="n">
-        <v>47074</v>
+        <v>57074</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>34629.52</v>
+        <v>44629.52</v>
       </c>
     </row>
     <row r="23">
@@ -1187,11 +1187,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>318564</v>
+        <v>397384</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>113.8%</t>
+          <t>141.9%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>226176</v>
+        <v>304996</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>65386.01</v>
+        <v>87986.00999999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>58388.01</v>
+        <v>80988.00999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>166153.01</v>
+        <v>166949.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>227.6%</t>
+          <t>228.7%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>143753.01</v>
+        <v>144549.01</v>
       </c>
     </row>
     <row r="26">
@@ -1323,11 +1323,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>133544</v>
+        <v>143942</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>133.5%</t>
+          <t>143.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>125544</v>
+        <v>135942</v>
       </c>
     </row>
     <row r="28">
@@ -1459,11 +1459,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>90364.2</v>
+        <v>98364.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1471,11 +1471,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>85866.2</v>
+        <v>93866.2</v>
       </c>
     </row>
     <row r="32">
@@ -1561,11 +1561,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>148184</v>
+        <v>148582</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>147954</v>
+        <v>148352</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>28988</v>
+        <v>29386</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>28988</v>
+        <v>29386</v>
       </c>
     </row>
     <row r="36">
@@ -1697,11 +1697,11 @@
         <v>40000</v>
       </c>
       <c r="D38" t="n">
-        <v>48192</v>
+        <v>49192</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>120.5%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>48192</v>
+        <v>49192</v>
       </c>
     </row>
     <row r="39">
@@ -1833,11 +1833,11 @@
         <v>200000</v>
       </c>
       <c r="D42" t="n">
-        <v>21796</v>
+        <v>31796</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>115.6%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-3404</v>
+        <v>6596</v>
       </c>
     </row>
     <row r="43">
@@ -1901,11 +1901,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>230844</v>
+        <v>240844</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>153.9%</t>
+          <t>160.6%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>230844</v>
+        <v>240844</v>
       </c>
     </row>
     <row r="45">
@@ -2173,23 +2173,23 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>113682</v>
+        <v>123182</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>102.7%</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>28800</v>
+        <v>34400</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>84882</v>
+        <v>88782</v>
       </c>
     </row>
     <row r="53">
@@ -2207,23 +2207,23 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>134464</v>
+        <v>170862</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>16800</v>
+        <v>41600</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>117664</v>
+        <v>129262</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>69592</v>
+        <v>107592</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>100.2%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>69592</v>
+        <v>107592</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>48000</v>
       </c>
       <c r="D55" t="n">
-        <v>13796</v>
+        <v>34796</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>13796</v>
+        <v>34796</v>
       </c>
     </row>
     <row r="56">
@@ -2343,11 +2343,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>70284</v>
+        <v>78682</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>62284</v>
+        <v>70682</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>89972</v>
+        <v>106370</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>55172</v>
+        <v>71570</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>134962</v>
+        <v>150962</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>112.5%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2423,11 +2423,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>124762</v>
+        <v>140762</v>
       </c>
     </row>
     <row r="60">
@@ -2479,11 +2479,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>316931.5</v>
+        <v>388931.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2491,11 +2491,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>296931.5</v>
+        <v>368931.5</v>
       </c>
     </row>
     <row r="62">
@@ -2513,23 +2513,23 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>66169.62</v>
+        <v>166073.12</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>15212</v>
+        <v>25212</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>50957.62</v>
+        <v>140861.12</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>181673.48</v>
+        <v>206071.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2559,11 +2559,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>144673.48</v>
+        <v>169071.48</v>
       </c>
     </row>
     <row r="64">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,57 +461,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>陈新星</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>134000</v>
+        <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>53449</v>
+        <v>36387.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>15218</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>38231</v>
+        <v>36387.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>田婉丽</t>
+          <t>田奇</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>143880</v>
+        <v>603.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>143.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,29 +523,29 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>143880</v>
+        <v>603.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>罗晗</t>
+          <t>李明</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24000</v>
+        <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>46868</v>
+        <v>15398</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>195.3%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,29 +557,29 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>46868</v>
+        <v>15398</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>林峻民</t>
+          <t>苏怡意</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32000</v>
+        <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>9184</v>
+        <v>290.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -591,29 +591,29 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9184</v>
+        <v>290.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>朱锋剑</t>
+          <t>姜玮</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90000</v>
+        <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>18796</v>
+        <v>10392.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,41 +625,41 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>18796</v>
+        <v>10392.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>孙君兰</t>
+          <t>李家慧</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>130000</v>
+        <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>73224.69</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>72904.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -670,30 +670,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>孙君兰</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>133200</v>
+        <v>1200</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>18150</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>115050</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="9">
@@ -708,26 +708,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>138885.26</v>
+        <v>8200</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>115.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>142900</v>
+        <v>200</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>102.9%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-4014.739999999991</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="10">
@@ -738,30 +738,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>米兰兰</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>60000</v>
+        <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>44100</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>41000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -772,18 +772,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>胡梦莉</t>
+          <t>米兰兰</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,29 +795,29 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>307177.14</v>
+        <v>7500</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>102.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,29 +829,29 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>307177.14</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>朱锋剑</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="D13" t="n">
-        <v>145375.5700000001</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -863,29 +863,29 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>145375.5700000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>400000</v>
+        <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>468749.74</v>
+        <v>20598</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>117.2%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,33 +897,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>468749.74</v>
+        <v>20598</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>250000</v>
+        <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>206846.74</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -931,29 +931,29 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>206846.74</v>
+        <v>-398</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>朱碧丹</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>250000</v>
+        <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>190303</v>
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,29 +965,29 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>190303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>王钰尧</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>300000</v>
+        <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>270507</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,29 +999,29 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>270507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>唐晟</t>
+          <t>邓璐</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>50000</v>
+        <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>19174</v>
+        <v>1500</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,33 +1033,33 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>19174</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>马雅丽</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>200000</v>
+        <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>127871</v>
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1067,29 +1067,29 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>127871</v>
+        <v>-5000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>王凯</t>
+          <t>周思若</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>50000</v>
+        <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>33596</v>
+        <v>1542</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,29 +1101,29 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>33596</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>韩雪</t>
+          <t>袁登玉</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>91172</v>
+        <v>7920</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,165 +1135,165 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>91172</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>邝玉萍</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="D22" t="n">
-        <v>57074</v>
+        <v>0</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12444.48</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>44629.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>280000</v>
+        <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>397384</v>
+        <v>33992</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>141.9%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>92388</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>304996</v>
+        <v>33992</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>白蕾</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="D24" t="n">
-        <v>87986.00999999999</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6998</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>80988.00999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>刘沁</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>166949.01</v>
+        <v>2394</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>228.7%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>22400</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>144549.01</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>余婉丽</t>
+          <t>芊雅</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>11958</v>
+        <v>0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,97 +1305,97 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>11958</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>王秋</t>
+          <t>刘馨</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>143942</v>
+        <v>10000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>143.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>135942</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>陈月娇</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>270000</v>
+        <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>274354.45</v>
+        <v>398</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>101.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>40580</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>233774.45</v>
+        <v>398</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>田奇</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>118406.9</v>
+        <v>1800</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,199 +1407,199 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>118406.9</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>杨红瑞</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>99084</v>
+        <v>4980</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>86084</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>苏怡意</t>
+          <t>普元媛</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>160000</v>
+        <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>98364.2</v>
+        <v>398</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4498</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>93866.2</v>
+        <v>398</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>马奇君</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>130000</v>
+        <v>30000</v>
       </c>
       <c r="D32" t="n">
-        <v>51804</v>
+        <v>398</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>43804</v>
+        <v>398</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>李家慧</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>50000</v>
+        <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>8398</v>
+        <v>10996</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>8398</v>
+        <v>6996</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>120000</v>
+        <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>148582</v>
+        <v>44562.32</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>148352</v>
+        <v>44562.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>李颜君</t>
+          <t>陈舒羽</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>40000</v>
+        <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>29386</v>
+        <v>10598</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,29 +1611,29 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29386</v>
+        <v>10598</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>谌黎平</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>40000</v>
+        <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>110266</v>
+        <v>10000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>275.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,63 +1645,63 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>110266</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>马春兰</t>
+          <t>张回</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="D37" t="n">
-        <v>42786</v>
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>41106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>冯兰兰</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="D38" t="n">
-        <v>49192</v>
+        <v>0</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,29 +1713,29 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>49192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>吴静文</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="D39" t="n">
         <v>398</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1753,125 +1753,125 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>许冰</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>170000</v>
+        <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>140186</v>
+        <v>106598</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>8800</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>131386</v>
+        <v>106598</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>白蕾</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>77782</v>
+        <v>398</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>67782</v>
+        <v>398</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>王芊雅</t>
+          <t>王秋</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>200000</v>
+        <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>31796</v>
+        <v>398</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>25200</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>6596</v>
+        <v>398</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>刘沁</t>
+          <t>陈翔宇</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>150000</v>
+        <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>105650</v>
+        <v>1980</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,29 +1883,29 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>105650</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>余婉丽</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>150000</v>
+        <v>50000</v>
       </c>
       <c r="D44" t="n">
-        <v>240844</v>
+        <v>1000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>160.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1917,29 +1917,29 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>240844</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>200000</v>
+        <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>194663.28</v>
+        <v>5207</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,29 +1951,29 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>194663.28</v>
+        <v>5207</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>韩雪</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>173294</v>
+        <v>1980</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1985,63 +1985,63 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>173294</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>陈舒羽</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>101372</v>
+        <v>7810</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>16800</v>
+        <v>0</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>84572</v>
+        <v>7810</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>沈悦</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>120000</v>
+        <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>72218</v>
+        <v>0</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,63 +2053,63 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>72218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>尹欢</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>120000</v>
+        <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>8398</v>
+        <v>31234</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1998</v>
+        <v>31234</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>庄鑫</t>
+          <t>唐晟</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2121,29 +2121,29 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>张回</t>
+          <t>王凯</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10000</v>
+        <v>80000</v>
       </c>
       <c r="D51" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2155,97 +2155,97 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>陈月娇</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>120000</v>
+        <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>123182</v>
+        <v>33994</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>102.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>34400</v>
+        <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>88782</v>
+        <v>33994</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>210000</v>
+        <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>170862</v>
+        <v>12104.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>41600</v>
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>129262</v>
+        <v>12104.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>杨红瑞</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>107400</v>
+        <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>107592</v>
+        <v>51980</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>100.2%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,29 +2257,29 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>107592</v>
+        <v>51980</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>普元媛</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>48000</v>
+        <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>34796</v>
+        <v>398</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,29 +2291,29 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>34796</v>
+        <v>398</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>马奇君</t>
+          <t>谌黎平</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>20000</v>
+        <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>7998</v>
+        <v>30796</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2325,131 +2325,131 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>7998</v>
+        <v>30796</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>马春兰</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>78682</v>
+        <v>10000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>70682</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>李颜君</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="D58" t="n">
-        <v>106370</v>
+        <v>0</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>34800</v>
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>71570</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>朱碧丹</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>150962</v>
+        <v>0</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>10200</v>
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>140762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>王钰尧</t>
+          <t>吴静文</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="D60" t="n">
-        <v>28584</v>
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,177 +2461,109 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>28584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>陈新星</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>334800</v>
+        <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>388931.5</v>
+        <v>0</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>368931.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>马雅丽</t>
+          <t>田婉丽</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>204401</v>
+        <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>166073.12</v>
+        <v>29497</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>25212</v>
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>140861.12</v>
+        <v>29497</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>周思若</t>
+          <t>罗晗</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>259200</v>
+        <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>206071.48</v>
+        <v>7880</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>131.3%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>169071.48</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>袁登玉</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>20796</v>
-      </c>
-      <c r="D64" t="n">
-        <v>796</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>邝玉萍</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>15378</v>
-      </c>
-      <c r="D65" t="n">
-        <v>17394</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>113.1%</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>17394</v>
+        <v>7880</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -1282,18 +1282,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>芊雅</t>
+          <t>王芊雅</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="27">
@@ -1932,14 +1932,14 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>270000</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>5207</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1966,14 +1966,14 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>1980</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2000,14 +2000,14 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>7810</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>210000</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2068,14 +2068,14 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>230000</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>31234</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2102,14 +2102,14 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
         <v>398</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2170,14 +2170,14 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
         <v>33994</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2204,14 +2204,14 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>12104.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2238,14 +2238,14 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>240000</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
         <v>51980</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F54" t="n">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,23 +473,23 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>36387.2</v>
+        <v>50001.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>36387.2</v>
+        <v>47001.4</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>603.2</v>
+        <v>18503.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>603.2</v>
+        <v>18503.2</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>15398</v>
+        <v>19298</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>15398</v>
+        <v>19298</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>290.3</v>
+        <v>6290.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>290.3</v>
+        <v>5190.3</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>10392.7</v>
+        <v>21230.88</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10392.7</v>
+        <v>21230.88</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="8">
@@ -677,11 +677,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>1200</v>
+        <v>13829.91</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1200</v>
+        <v>13829.91</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>8200</v>
+        <v>20636.43</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>8000</v>
+        <v>20436.43</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>18598</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>18598</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>3900</v>
+        <v>7000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3900</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>7500</v>
+        <v>18900</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7500</v>
+        <v>18900</v>
       </c>
     </row>
     <row r="13">
@@ -881,11 +881,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>20598</v>
+        <v>33196</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20598</v>
+        <v>33196</v>
       </c>
     </row>
     <row r="15">
@@ -915,11 +915,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>9996</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -927,11 +927,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-398</v>
+        <v>9598</v>
       </c>
     </row>
     <row r="16">
@@ -949,11 +949,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>996</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>996</v>
       </c>
     </row>
     <row r="17">
@@ -983,11 +983,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="18">
@@ -1017,11 +1017,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>1500</v>
+        <v>1951.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1500</v>
+        <v>1951.8</v>
       </c>
     </row>
     <row r="19">
@@ -1051,11 +1051,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>33634.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-5000</v>
+        <v>28634.9</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>1542</v>
+        <v>22737.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1542</v>
+        <v>22737.5</v>
       </c>
     </row>
     <row r="21">
@@ -1119,11 +1119,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>7920</v>
+        <v>18318</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7920</v>
+        <v>18318</v>
       </c>
     </row>
     <row r="22">
@@ -1187,11 +1187,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>33992</v>
+        <v>58390</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>33992</v>
+        <v>58390</v>
       </c>
     </row>
     <row r="24">
@@ -1221,11 +1221,11 @@
         <v>150000</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="25">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>2394</v>
+        <v>7772</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2394</v>
+        <v>7772</v>
       </c>
     </row>
     <row r="26">
@@ -1289,11 +1289,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>4980</v>
+        <v>20358</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4980</v>
+        <v>20358</v>
       </c>
     </row>
     <row r="27">
@@ -1361,19 +1361,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>4999.98</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1256.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>398</v>
+        <v>-4601.98</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>1800</v>
+        <v>41786</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1800</v>
+        <v>41786</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>4980</v>
+        <v>15378</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4980</v>
+        <v>15378</v>
       </c>
     </row>
     <row r="31">
@@ -1459,11 +1459,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>398</v>
+        <v>2098</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>398</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="32">
@@ -1527,23 +1527,23 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>10996</v>
+        <v>53292</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4000</v>
+        <v>33800</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6996</v>
+        <v>19492</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>44562.32</v>
+        <v>55715.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>44562.32</v>
+        <v>55715.6</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>10598</v>
+        <v>21549</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>10598</v>
+        <v>21549</v>
       </c>
     </row>
     <row r="36">
@@ -1731,11 +1731,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>398</v>
+        <v>21076</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>398</v>
+        <v>21076</v>
       </c>
     </row>
     <row r="40">
@@ -1765,11 +1765,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>106598</v>
+        <v>174296</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>106598</v>
+        <v>174296</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>398</v>
+        <v>3097</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>398</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>398</v>
+        <v>9996</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>398</v>
+        <v>9996</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>1980</v>
+        <v>3174</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1980</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="44">
@@ -1935,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>5207</v>
+        <v>21352.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5207</v>
+        <v>21352.5</v>
       </c>
     </row>
     <row r="46">
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>7810</v>
+        <v>43009</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>7810</v>
+        <v>43009</v>
       </c>
     </row>
     <row r="48">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>20573</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>20573</v>
       </c>
     </row>
     <row r="49">
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>31234</v>
+        <v>69017</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>31234</v>
+        <v>69017</v>
       </c>
     </row>
     <row r="50">
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="52">
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>33994</v>
+        <v>81667</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>33994</v>
+        <v>81667</v>
       </c>
     </row>
     <row r="53">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>12104.1</v>
+        <v>43848.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>12104.1</v>
+        <v>43848.1</v>
       </c>
     </row>
     <row r="54">
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>51980</v>
+        <v>93072</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>51980</v>
+        <v>93072</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>398</v>
+        <v>796</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>398</v>
+        <v>796</v>
       </c>
     </row>
     <row r="56">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>10000</v>
+        <v>22378</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>10000</v>
+        <v>22378</v>
       </c>
     </row>
     <row r="58">
@@ -2411,11 +2411,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>28412</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>28412</v>
       </c>
     </row>
     <row r="60">
@@ -2445,11 +2445,11 @@
         <v>20000</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="61">
@@ -2479,11 +2479,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>23398</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>23398</v>
       </c>
     </row>
     <row r="62">
@@ -2513,11 +2513,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>29497</v>
+        <v>44497</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>29497</v>
+        <v>44497</v>
       </c>
     </row>
     <row r="63">
@@ -2547,11 +2547,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>7880</v>
+        <v>8278</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>131.3%</t>
+          <t>138.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>7880</v>
+        <v>8278</v>
       </c>
     </row>
   </sheetData>

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -477,19 +477,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3000</v>
+        <v>22866.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47001.4</v>
+        <v>27134.73</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>18503.2</v>
+        <v>21603.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>18503.2</v>
+        <v>21603.2</v>
       </c>
     </row>
     <row r="4">
@@ -609,11 +609,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>21230.88</v>
+        <v>22335.36</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>21230.88</v>
+        <v>22335.36</v>
       </c>
     </row>
     <row r="7">
@@ -711,11 +711,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>20636.43</v>
+        <v>21382.13</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -723,11 +723,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>20436.43</v>
+        <v>21182.13</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +745,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>18598</v>
+        <v>35796</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>18598</v>
+        <v>35796</v>
       </c>
     </row>
     <row r="11">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>7000</v>
+        <v>7800</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="12">
@@ -949,11 +949,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>996</v>
+        <v>12996</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>996</v>
+        <v>12996</v>
       </c>
     </row>
     <row r="17">
@@ -1017,11 +1017,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>1951.8</v>
+        <v>2530.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1951.8</v>
+        <v>2530.6</v>
       </c>
     </row>
     <row r="19">
@@ -1085,11 +1085,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>22737.5</v>
+        <v>33751.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>22737.5</v>
+        <v>33751.8</v>
       </c>
     </row>
     <row r="21">
@@ -1255,23 +1255,23 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>7772</v>
+        <v>53160</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7772</v>
+        <v>43360</v>
       </c>
     </row>
     <row r="26">
@@ -1357,23 +1357,23 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>398</v>
+        <v>996</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4999.98</v>
+        <v>8999.98</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1256.3%</t>
+          <t>903.6%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-4601.98</v>
+        <v>-8003.98</v>
       </c>
     </row>
     <row r="29">
@@ -1459,11 +1459,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>2098</v>
+        <v>12098</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2098</v>
+        <v>12098</v>
       </c>
     </row>
     <row r="32">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>55715.6</v>
+        <v>49715.6</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>21549</v>
+        <v>31549</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>21549</v>
+        <v>31549</v>
       </c>
     </row>
     <row r="36">
@@ -1731,11 +1731,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>21076</v>
+        <v>21474</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>21076</v>
+        <v>21474</v>
       </c>
     </row>
     <row r="40">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>3097</v>
+        <v>3795</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3097</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="42">
@@ -1867,11 +1867,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>3174</v>
+        <v>33572</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3174</v>
+        <v>33572</v>
       </c>
     </row>
     <row r="44">
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>43009</v>
+        <v>53407</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>43009</v>
+        <v>53407</v>
       </c>
     </row>
     <row r="48">
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>81667</v>
+        <v>78324</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>81667</v>
+        <v>78324</v>
       </c>
     </row>
     <row r="53">
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>93072</v>
+        <v>104114</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>93072</v>
+        <v>104114</v>
       </c>
     </row>
     <row r="55">
@@ -2275,11 +2275,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>796</v>
+        <v>5796</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>796</v>
+        <v>5796</v>
       </c>
     </row>
     <row r="56">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>22378</v>
+        <v>24058</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>22378</v>
+        <v>24058</v>
       </c>
     </row>
     <row r="58">
@@ -2377,11 +2377,11 @@
         <v>60000</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="59">
@@ -2411,11 +2411,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>28412</v>
+        <v>38412</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>28412</v>
+        <v>38412</v>
       </c>
     </row>
     <row r="60">
@@ -2479,11 +2479,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>23398</v>
+        <v>24194</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>23398</v>
+        <v>24194</v>
       </c>
     </row>
     <row r="62">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -1932,14 +1932,14 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>270000</v>
       </c>
       <c r="D45" t="n">
         <v>21352.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1966,14 +1966,14 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="D46" t="n">
         <v>1980</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2000,14 +2000,14 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="D47" t="n">
         <v>53407</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2034,14 +2034,14 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="D48" t="n">
         <v>20573</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2068,14 +2068,14 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="D49" t="n">
         <v>69017</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2102,14 +2102,14 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="D50" t="n">
         <v>398</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2136,14 +2136,14 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="D51" t="n">
         <v>10000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2170,14 +2170,14 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="D52" t="n">
         <v>78324</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2204,14 +2204,14 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>220000</v>
       </c>
       <c r="D53" t="n">
         <v>43848.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2238,14 +2238,14 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="D54" t="n">
         <v>104114</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="F54" t="n">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>50001.4</v>
+        <v>58568.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>27134.73</v>
+        <v>35701.53</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>19298</v>
+        <v>26798</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>19298</v>
+        <v>26798</v>
       </c>
     </row>
     <row r="5">
@@ -575,23 +575,23 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>6290.3</v>
+        <v>6688.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1100</v>
+        <v>2600</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5190.3</v>
+        <v>4088.3</v>
       </c>
     </row>
     <row r="6">
@@ -677,11 +677,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>13829.91</v>
+        <v>15029.91</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>13829.91</v>
+        <v>15029.91</v>
       </c>
     </row>
     <row r="9">
@@ -711,11 +711,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>21382.13</v>
+        <v>21687.13</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>21182.13</v>
+        <v>21487.13</v>
       </c>
     </row>
     <row r="10">
@@ -813,11 +813,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>18900</v>
+        <v>22800</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>18900</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="13">
@@ -1051,11 +1051,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>33634.9</v>
+        <v>45877.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>28634.9</v>
+        <v>40877.8</v>
       </c>
     </row>
     <row r="20">
@@ -1085,23 +1085,23 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>33751.8</v>
+        <v>34149.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>33751.8</v>
+        <v>30149.8</v>
       </c>
     </row>
     <row r="21">
@@ -1187,11 +1187,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>58390</v>
+        <v>68390</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>58390</v>
+        <v>68390</v>
       </c>
     </row>
     <row r="24">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>53160</v>
+        <v>61966</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>43360</v>
+        <v>52166</v>
       </c>
     </row>
     <row r="26">
@@ -1357,23 +1357,23 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>996</v>
+        <v>12996</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8999.98</v>
+        <v>19399.98</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>903.6%</t>
+          <t>149.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-8003.98</v>
+        <v>-6403.98</v>
       </c>
     </row>
     <row r="29">
@@ -1391,11 +1391,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>41786</v>
+        <v>79984</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>41786</v>
+        <v>79984</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>15378</v>
+        <v>15976</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>15378</v>
+        <v>15976</v>
       </c>
     </row>
     <row r="31">
@@ -1527,11 +1527,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>53292</v>
+        <v>57029.78</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>19492</v>
+        <v>23229.78</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>55715.6</v>
+        <v>56511.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>49715.6</v>
+        <v>50511.6</v>
       </c>
     </row>
     <row r="35">
@@ -1595,11 +1595,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>31549</v>
+        <v>43549</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>31549</v>
+        <v>43549</v>
       </c>
     </row>
     <row r="36">
@@ -1697,11 +1697,11 @@
         <v>30000</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
     </row>
     <row r="39">
@@ -1765,23 +1765,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>174296</v>
+        <v>174694</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>174296</v>
+        <v>162694</v>
       </c>
     </row>
     <row r="41">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>3795</v>
+        <v>10395</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3795</v>
+        <v>10395</v>
       </c>
     </row>
     <row r="42">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>9996</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>33572</v>
+        <v>35252</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>33572</v>
+        <v>35252</v>
       </c>
     </row>
     <row r="44">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>21352.5</v>
+        <v>21906.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>21352.5</v>
+        <v>21906.5</v>
       </c>
     </row>
     <row r="46">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>53407</v>
+        <v>61082</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>53407</v>
+        <v>61082</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>20573</v>
+        <v>30573</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>20573</v>
+        <v>30573</v>
       </c>
     </row>
     <row r="49">
@@ -2207,11 +2207,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>43848.1</v>
+        <v>44106.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>43848.1</v>
+        <v>44106.1</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>104114</v>
+        <v>114114</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>104114</v>
+        <v>114114</v>
       </c>
     </row>
     <row r="55">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>24058</v>
+        <v>34058</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>24058</v>
+        <v>34058</v>
       </c>
     </row>
     <row r="58">
@@ -2411,11 +2411,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>38412</v>
+        <v>48810</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>38412</v>
+        <v>48810</v>
       </c>
     </row>
     <row r="60">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>58568.2</v>
+        <v>78568.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>35701.53</v>
+        <v>55701.53</v>
       </c>
     </row>
     <row r="3">
@@ -507,11 +507,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>21603.2</v>
+        <v>29303.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>21603.2</v>
+        <v>29303.2</v>
       </c>
     </row>
     <row r="4">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>26798</v>
+        <v>29898</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>26798</v>
+        <v>29898</v>
       </c>
     </row>
     <row r="5">
@@ -575,11 +575,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>6688.3</v>
+        <v>7086.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4088.3</v>
+        <v>4486.3</v>
       </c>
     </row>
     <row r="6">
@@ -609,11 +609,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>22335.36</v>
+        <v>27733.36</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>22335.36</v>
+        <v>27733.36</v>
       </c>
     </row>
     <row r="7">
@@ -643,11 +643,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>10398</v>
+        <v>10796</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10398</v>
+        <v>10796</v>
       </c>
     </row>
     <row r="8">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>7800</v>
+        <v>10320</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7800</v>
+        <v>10320</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>22800</v>
+        <v>30300</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>22800</v>
+        <v>30300</v>
       </c>
     </row>
     <row r="13">
@@ -881,11 +881,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>33196</v>
+        <v>72784</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>33196</v>
+        <v>72784</v>
       </c>
     </row>
     <row r="15">
@@ -1255,11 +1255,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>61966</v>
+        <v>77966</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1267,11 +1267,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>52166</v>
+        <v>68166</v>
       </c>
     </row>
     <row r="26">
@@ -1493,11 +1493,11 @@
         <v>30000</v>
       </c>
       <c r="D32" t="n">
-        <v>398</v>
+        <v>10796</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>398</v>
+        <v>10796</v>
       </c>
     </row>
     <row r="33">
@@ -1527,11 +1527,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>57029.78</v>
+        <v>70181.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1539,11 +1539,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>23229.78</v>
+        <v>36381.64</v>
       </c>
     </row>
     <row r="34">
@@ -1561,11 +1561,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>56511.6</v>
+        <v>67279.75999999999</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>50511.6</v>
+        <v>61279.75999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1629,11 +1629,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>10000</v>
+        <v>10398</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10000</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="37">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>10395</v>
+        <v>18395</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>10395</v>
+        <v>18395</v>
       </c>
     </row>
     <row r="42">
@@ -1935,11 +1935,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>21906.5</v>
+        <v>23481.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>21906.5</v>
+        <v>23481.5</v>
       </c>
     </row>
     <row r="46">
@@ -2003,11 +2003,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>61082</v>
+        <v>66477</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>61082</v>
+        <v>66477</v>
       </c>
     </row>
     <row r="48">
@@ -2037,11 +2037,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>30573</v>
+        <v>25791</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>30573</v>
+        <v>25791</v>
       </c>
     </row>
     <row r="49">
@@ -2071,11 +2071,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>69017</v>
+        <v>95807</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>69017</v>
+        <v>95807</v>
       </c>
     </row>
     <row r="50">
@@ -2139,11 +2139,11 @@
         <v>80000</v>
       </c>
       <c r="D51" t="n">
-        <v>10000</v>
+        <v>15940</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>10000</v>
+        <v>15940</v>
       </c>
     </row>
     <row r="52">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>78324</v>
+        <v>90504</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>78324</v>
+        <v>90504</v>
       </c>
     </row>
     <row r="53">
@@ -2207,11 +2207,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>44106.1</v>
+        <v>35106.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>44106.1</v>
+        <v>35106.1</v>
       </c>
     </row>
     <row r="54">
@@ -2241,11 +2241,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>114114</v>
+        <v>130278</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>114114</v>
+        <v>130278</v>
       </c>
     </row>
     <row r="55">
@@ -2279,19 +2279,19 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>172.5%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>5796</v>
+        <v>-4204</v>
       </c>
     </row>
     <row r="56">
@@ -2517,19 +2517,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>44497</v>
+        <v>37697</v>
       </c>
     </row>
     <row r="63">

--- a/导出_线下个案.xlsx
+++ b/导出_线下个案.xlsx
@@ -473,11 +473,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>78568.2</v>
+        <v>83568.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -485,11 +485,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>55701.53</v>
+        <v>60701.53</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>29898</v>
+        <v>40296</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>29898</v>
+        <v>40296</v>
       </c>
     </row>
     <row r="5">
@@ -609,11 +609,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>27733.36</v>
+        <v>38529.36</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>27733.36</v>
+        <v>38529.36</v>
       </c>
     </row>
     <row r="7">
@@ -711,7 +711,7 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>21687.13</v>
+        <v>21695.11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>21487.13</v>
+        <v>21495.11</v>
       </c>
     </row>
     <row r="10">
@@ -779,11 +779,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>10320</v>
+        <v>7800</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10320</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="12">
@@ -813,11 +813,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>30300</v>
+        <v>33400</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>30300</v>
+        <v>33400</v>
       </c>
     </row>
     <row r="13">
@@ -983,11 +983,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>10398</v>
+        <v>11194</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>10398</v>
+        <v>11194</v>
       </c>
     </row>
     <row r="18">
@@ -1051,11 +1051,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>45877.8</v>
+        <v>47955.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1063,11 +1063,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>40877.8</v>
+        <v>42955.8</v>
       </c>
     </row>
     <row r="20">
@@ -1085,11 +1085,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>34149.8</v>
+        <v>54149.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>30149.8</v>
+        <v>50149.8</v>
       </c>
     </row>
     <row r="21">
@@ -1187,11 +1187,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>68390</v>
+        <v>74584</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>68390</v>
+        <v>74584</v>
       </c>
     </row>
     <row r="24">
@@ -1323,11 +1323,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>10000</v>
+        <v>20398</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>10000</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="28">
@@ -1391,23 +1391,23 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>79984</v>
+        <v>80382</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>79984</v>
+        <v>73382</v>
       </c>
     </row>
     <row r="30">
@@ -1425,11 +1425,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>15976</v>
+        <v>16176</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>15976</v>
+        <v>16176</v>
       </c>
     </row>
     <row r="31">
@@ -1599,19 +1599,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>43549</v>
+        <v>36949</v>
       </c>
     </row>
     <row r="36">
@@ -1731,11 +1731,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>21474</v>
+        <v>28074</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>21474</v>
+        <v>28074</v>
       </c>
     </row>
     <row r="40">
@@ -1799,11 +1799,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>18395</v>
+        <v>28395</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>18395</v>
+        <v>28395</v>
       </c>
     </row>
     <row r="42">
@@ -1833,11 +1833,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>9996</v>
+        <v>16596</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1845,11 +1845,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2396</v>
+        <v>8996</v>
       </c>
     </row>
     <row r="43">
@@ -1867,11 +1867,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>35252</v>
+        <v>35751</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>35252</v>
+        <v>35751</v>
       </c>
     </row>
     <row r="44">
@@ -2037,11 +2037,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>25791</v>
+        <v>27983</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>25791</v>
+        <v>27983</v>
       </c>
     </row>
     <row r="49">
@@ -2173,11 +2173,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>90504</v>
+        <v>91504</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>90504</v>
+        <v>91504</v>
       </c>
     </row>
     <row r="53">
@@ -2275,11 +2275,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>5796</v>
+        <v>26295</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2287,11 +2287,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>172.5%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>-4204</v>
+        <v>16295</v>
       </c>
     </row>
     <row r="56">
@@ -2343,11 +2343,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>34058</v>
+        <v>44058</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>34058</v>
+        <v>44058</v>
       </c>
     </row>
     <row r="58">
@@ -2411,11 +2411,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>48810</v>
+        <v>69208</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>115.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>48810</v>
+        <v>69208</v>
       </c>
     </row>
     <row r="60">
@@ -2517,19 +2517,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>6800</v>
+        <v>15800</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>37697</v>
+        <v>28697</v>
       </c>
     </row>
     <row r="63">
